--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21601"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hema.ananthan\eclipse-workspace\com.ggproduct.automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73E4C57D-9E24-4DFB-8238-B6FC35D99452}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D495E921-21F6-4BA9-8D0F-861C9F2CE4C5}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9060" activeTab="1" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -135,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -143,6 +143,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -459,14 +462,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756EB8E1-CDD7-4F47-B6A9-50B266C05D05}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -477,7 +480,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -488,7 +491,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -499,7 +502,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -510,7 +513,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -530,87 +533,87 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165F264A-263B-4AE4-BE30-B37BD58F47A5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="158" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="158" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="4">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="4">
         <v>-2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
       <c r="B7" t="s">
         <v>21</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="4" t="s">
         <v>22</v>
       </c>
     </row>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -1,20 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21901"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspace-Product-Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D495E921-21F6-4BA9-8D0F-861C9F2CE4C5}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A30F4E-0B7C-4C92-B79C-3C36FF75DC7C}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
-    <sheet name="Form Fields" sheetId="2" r:id="rId2"/>
+    <sheet name="ScheduleQuartelyCalendar" sheetId="3" r:id="rId2"/>
+    <sheet name="ScheduleAnnuallyCalendar" sheetId="4" r:id="rId3"/>
+    <sheet name="ScheduleSemiAnnually" sheetId="5" r:id="rId4"/>
+    <sheet name="ScheduleBiMonthly" sheetId="6" r:id="rId5"/>
+    <sheet name="Form Fields" sheetId="2" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="44">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -100,19 +104,94 @@
   </si>
   <si>
     <t>the space below, provide details of the information that was presented to the board:</t>
+  </si>
+  <si>
+    <t>SubmissionTitle__c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation Progress Report </t>
+  </si>
+  <si>
+    <t>Frequency__c</t>
+  </si>
+  <si>
+    <t>ScheduleBase__c</t>
+  </si>
+  <si>
+    <t>Description__c</t>
+  </si>
+  <si>
+    <t>Automation Test Description</t>
+  </si>
+  <si>
+    <t>CalReportingStartDate__c</t>
+  </si>
+  <si>
+    <t>CalReportingEndDate__c</t>
+  </si>
+  <si>
+    <t>Calendar</t>
+  </si>
+  <si>
+    <t>08/25/2023</t>
+  </si>
+  <si>
+    <t>08/25/2024</t>
+  </si>
+  <si>
+    <t>Quarterly</t>
+  </si>
+  <si>
+    <t>Semi-Annually</t>
+  </si>
+  <si>
+    <t>01/08/2021</t>
+  </si>
+  <si>
+    <t>01/12/2022</t>
+  </si>
+  <si>
+    <t>01/09/2021</t>
+  </si>
+  <si>
+    <t>Bi-Monthly</t>
+  </si>
+  <si>
+    <t>12/01/2021</t>
+  </si>
+  <si>
+    <t>09/01/2023</t>
+  </si>
+  <si>
+    <t>12/01/2024</t>
+  </si>
+  <si>
+    <t>Annually</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF212121"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -135,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -147,6 +226,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -531,6 +613,407 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9083A037-5F1C-4F1B-BC9C-BD3BCDD5C4F5}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B602DAF3-EA4C-4411-83F6-DC18D5FF0624}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7AE48B-043F-4B46-920A-8E923AEFDF07}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6733A2-29DF-4936-8F0F-DBCC59247680}">
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I17" s="1"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="7"/>
+    </row>
+    <row r="19" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="6"/>
+    </row>
+    <row r="22" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165F264A-263B-4AE4-BE30-B37BD58F47A5}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17A30F4E-0B7C-4C92-B79C-3C36FF75DC7C}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612E53E8-2C44-4FD4-96B7-FEE0B9738D57}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="1" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -1,24 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{612E53E8-2C44-4FD4-96B7-FEE0B9738D57}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC629CC9-44C2-40B9-A3B6-E0C94806CB53}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="1" activeTab="2" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
-    <sheet name="ScheduleQuartelyCalendar" sheetId="3" r:id="rId2"/>
-    <sheet name="ScheduleAnnuallyCalendar" sheetId="4" r:id="rId3"/>
-    <sheet name="ScheduleSemiAnnually" sheetId="5" r:id="rId4"/>
-    <sheet name="ScheduleBiMonthly" sheetId="6" r:id="rId5"/>
-    <sheet name="Form Fields" sheetId="2" r:id="rId6"/>
+    <sheet name="PlanError" sheetId="10" r:id="rId2"/>
+    <sheet name="ObstacleError" sheetId="9" r:id="rId3"/>
+    <sheet name="KeyAccError" sheetId="8" r:id="rId4"/>
+    <sheet name="ErrorForAck" sheetId="7" r:id="rId5"/>
+    <sheet name="ScheduleQuartelyCalendar" sheetId="3" r:id="rId6"/>
+    <sheet name="ScheduleAnnuallyCalendar" sheetId="4" r:id="rId7"/>
+    <sheet name="ScheduleSemiAnnually" sheetId="5" r:id="rId8"/>
+    <sheet name="ScheduleBiMonthly" sheetId="6" r:id="rId9"/>
+    <sheet name="Form Fields" sheetId="2" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="44">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -612,408 +616,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9083A037-5F1C-4F1B-BC9C-BD3BCDD5C4F5}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B602DAF3-EA4C-4411-83F6-DC18D5FF0624}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7AE48B-043F-4B46-920A-8E923AEFDF07}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6733A2-29DF-4936-8F0F-DBCC59247680}">
-  <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I17" s="1"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="7"/>
-    </row>
-    <row r="19" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-    </row>
-    <row r="21" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="6"/>
-    </row>
-    <row r="22" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="6"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165F264A-263B-4AE4-BE30-B37BD58F47A5}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1103,4 +706,643 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CB41D5-3EB7-4F7C-BAA0-9B20DD4811C4}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72F519A-34E9-47C6-868B-C146DEA726AE}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439DE0DC-8395-49F9-9A33-3B799989CDF9}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC6C784-F6B5-426A-A91D-7FBF6EF20C65}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9083A037-5F1C-4F1B-BC9C-BD3BCDD5C4F5}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B602DAF3-EA4C-4411-83F6-DC18D5FF0624}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7AE48B-043F-4B46-920A-8E923AEFDF07}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6733A2-29DF-4936-8F0F-DBCC59247680}">
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I17" s="1"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="7"/>
+    </row>
+    <row r="19" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="6"/>
+    </row>
+    <row r="22" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC629CC9-44C2-40B9-A3B6-E0C94806CB53}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82BA85F-D6BE-4B0E-ADAA-7000C92263A0}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="6" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -19,10 +19,11 @@
     <sheet name="KeyAccError" sheetId="8" r:id="rId4"/>
     <sheet name="ErrorForAck" sheetId="7" r:id="rId5"/>
     <sheet name="ScheduleQuartelyCalendar" sheetId="3" r:id="rId6"/>
-    <sheet name="ScheduleAnnuallyCalendar" sheetId="4" r:id="rId7"/>
-    <sheet name="ScheduleSemiAnnually" sheetId="5" r:id="rId8"/>
-    <sheet name="ScheduleBiMonthly" sheetId="6" r:id="rId9"/>
-    <sheet name="Form Fields" sheetId="2" r:id="rId10"/>
+    <sheet name="ProgressReportCalendarSchedule" sheetId="11" r:id="rId7"/>
+    <sheet name="ScheduleAnnuallyCalendar" sheetId="4" r:id="rId8"/>
+    <sheet name="ScheduleSemiAnnually" sheetId="5" r:id="rId9"/>
+    <sheet name="ScheduleBiMonthly" sheetId="6" r:id="rId10"/>
+    <sheet name="Form Fields" sheetId="2" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="47">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -171,6 +172,15 @@
   </si>
   <si>
     <t>Annually</t>
+  </si>
+  <si>
+    <t>Monthly</t>
+  </si>
+  <si>
+    <t>12/31/2023</t>
+  </si>
+  <si>
+    <t>1/01/2023</t>
   </si>
 </sst>
 </file>
@@ -218,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -233,6 +243,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -617,6 +628,133 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6733A2-29DF-4936-8F0F-DBCC59247680}">
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="3"/>
+    </row>
+    <row r="17" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I17" s="1"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="1"/>
+    </row>
+    <row r="18" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="7"/>
+    </row>
+    <row r="19" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+    </row>
+    <row r="20" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+    </row>
+    <row r="21" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="6"/>
+    </row>
+    <row r="22" spans="9:11" x14ac:dyDescent="0.25">
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="6"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165F264A-263B-4AE4-BE30-B37BD58F47A5}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1039,6 +1177,97 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8827C01F-82DB-4710-97BD-1D832235DF80}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B602DAF3-EA4C-4411-83F6-DC18D5FF0624}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1129,7 +1358,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7AE48B-043F-4B46-920A-8E923AEFDF07}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1218,131 +1447,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6733A2-29DF-4936-8F0F-DBCC59247680}">
-  <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I17" s="1"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="7"/>
-    </row>
-    <row r="19" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-    </row>
-    <row r="21" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="6"/>
-    </row>
-    <row r="22" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="6"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F82BA85F-D6BE-4B0E-ADAA-7000C92263A0}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE5D659-0BDE-45A6-BFFA-0B30589978AD}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="6" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" firstSheet="7" activeTab="11" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="ScheduleSemiAnnually" sheetId="5" r:id="rId9"/>
     <sheet name="ScheduleBiMonthly" sheetId="6" r:id="rId10"/>
     <sheet name="Form Fields" sheetId="2" r:id="rId11"/>
+    <sheet name="ErrorForm" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="47">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -559,14 +560,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756EB8E1-CDD7-4F47-B6A9-50B266C05D05}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.3046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.53515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -577,7 +578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -588,7 +589,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -599,7 +600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -610,7 +611,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -630,13 +631,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6733A2-29DF-4936-8F0F-DBCC59247680}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -647,7 +648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -658,7 +659,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -669,7 +670,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -680,7 +681,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -691,7 +692,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -702,7 +703,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -713,37 +714,37 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="3"/>
     </row>
-    <row r="17" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="9:11" x14ac:dyDescent="0.4">
       <c r="I17" s="1"/>
       <c r="J17" s="2"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="9:11" x14ac:dyDescent="0.4">
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="9:11" x14ac:dyDescent="0.4">
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="9:11" x14ac:dyDescent="0.4">
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="9:11" x14ac:dyDescent="0.4">
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="9:11" x14ac:dyDescent="0.4">
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="6"/>
@@ -757,14 +758,14 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165F264A-263B-4AE4-BE30-B37BD58F47A5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.3828125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="158" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -775,7 +776,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -786,7 +787,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -797,7 +798,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -808,7 +809,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -819,7 +820,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -830,7 +831,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -838,6 +839,71 @@
         <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDF5434-4D12-4F2F-B98B-154625A9FF1F}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="4">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>22</v>
       </c>
     </row>
@@ -849,15 +915,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CB41D5-3EB7-4F7C-BAA0-9B20DD4811C4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="11.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.3046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -868,7 +934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -879,7 +945,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -890,7 +956,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -909,15 +975,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72F519A-34E9-47C6-868B-C146DEA726AE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="11.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.3046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -928,7 +994,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -939,7 +1005,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -950,7 +1016,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -969,15 +1035,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439DE0DC-8395-49F9-9A33-3B799989CDF9}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="11.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.3046875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.53515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.15234375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -988,7 +1054,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -999,7 +1065,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1010,7 +1076,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1029,13 +1095,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC6C784-F6B5-426A-A91D-7FBF6EF20C65}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.3046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1046,7 +1112,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1057,7 +1123,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1068,7 +1134,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1087,13 +1153,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9083A037-5F1C-4F1B-BC9C-BD3BCDD5C4F5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1104,7 +1170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1115,7 +1181,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1126,7 +1192,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1137,7 +1203,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1148,7 +1214,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1159,7 +1225,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,13 +1245,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8827C01F-82DB-4710-97BD-1D832235DF80}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1196,7 +1262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1207,7 +1273,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1218,7 +1284,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1229,7 +1295,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1240,7 +1306,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1251,7 +1317,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1270,13 +1336,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B602DAF3-EA4C-4411-83F6-DC18D5FF0624}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1287,7 +1353,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1298,7 +1364,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1309,7 +1375,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1320,7 +1386,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1331,7 +1397,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1342,7 +1408,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1361,13 +1427,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7AE48B-043F-4B46-920A-8E923AEFDF07}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1378,7 +1444,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1389,7 +1455,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1400,7 +1466,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1411,7 +1477,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1422,7 +1488,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1433,7 +1499,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -5,26 +5,27 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MCPL#L92\Desktop\Automation projects\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCE5D659-0BDE-45A6-BFFA-0B30589978AD}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50F837A-0787-4387-83AE-0FC07562A5F0}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" firstSheet="7" activeTab="11" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="9" activeTab="12" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
-    <sheet name="PlanError" sheetId="10" r:id="rId2"/>
-    <sheet name="ObstacleError" sheetId="9" r:id="rId3"/>
-    <sheet name="KeyAccError" sheetId="8" r:id="rId4"/>
-    <sheet name="ErrorForAck" sheetId="7" r:id="rId5"/>
-    <sheet name="ScheduleQuartelyCalendar" sheetId="3" r:id="rId6"/>
-    <sheet name="ProgressReportCalendarSchedule" sheetId="11" r:id="rId7"/>
-    <sheet name="ScheduleAnnuallyCalendar" sheetId="4" r:id="rId8"/>
-    <sheet name="ScheduleSemiAnnually" sheetId="5" r:id="rId9"/>
-    <sheet name="ScheduleBiMonthly" sheetId="6" r:id="rId10"/>
-    <sheet name="Form Fields" sheetId="2" r:id="rId11"/>
-    <sheet name="ErrorForm" sheetId="12" r:id="rId12"/>
+    <sheet name="FinalProgressReport" sheetId="13" r:id="rId2"/>
+    <sheet name="PlanError" sheetId="10" r:id="rId3"/>
+    <sheet name="ObstacleError" sheetId="9" r:id="rId4"/>
+    <sheet name="KeyAccError" sheetId="8" r:id="rId5"/>
+    <sheet name="ErrorForAck" sheetId="7" r:id="rId6"/>
+    <sheet name="ScheduleQuartelyCalendar" sheetId="3" r:id="rId7"/>
+    <sheet name="ProgressReportCalendarSchedule" sheetId="11" r:id="rId8"/>
+    <sheet name="ScheduleAnnuallyCalendar" sheetId="4" r:id="rId9"/>
+    <sheet name="ScheduleSemiAnnually" sheetId="5" r:id="rId10"/>
+    <sheet name="ScheduleBiMonthly" sheetId="6" r:id="rId11"/>
+    <sheet name="Form Fields" sheetId="2" r:id="rId12"/>
+    <sheet name="ErrorForm" sheetId="12" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="48">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -182,6 +183,9 @@
   </si>
   <si>
     <t>1/01/2023</t>
+  </si>
+  <si>
+    <t>IsFinalReport__c</t>
   </si>
 </sst>
 </file>
@@ -560,14 +564,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756EB8E1-CDD7-4F47-B6A9-50B266C05D05}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.53515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.53515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -578,7 +582,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -589,7 +593,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -600,7 +604,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -611,7 +615,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -629,15 +633,15 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6733A2-29DF-4936-8F0F-DBCC59247680}">
-  <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7AE48B-043F-4B46-920A-8E923AEFDF07}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -648,7 +652,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -659,7 +663,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -667,10 +671,10 @@
         <v>25</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -681,7 +685,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -692,7 +696,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -700,10 +704,10 @@
         <v>29</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.4">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -711,40 +715,131 @@
         <v>30</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6733A2-29DF-4936-8F0F-DBCC59247680}">
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="3"/>
     </row>
-    <row r="17" spans="9:11" x14ac:dyDescent="0.4">
+    <row r="17" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I17" s="1"/>
       <c r="J17" s="2"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="9:11" x14ac:dyDescent="0.4">
+    <row r="18" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="9:11" x14ac:dyDescent="0.4">
+    <row r="19" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="9:11" x14ac:dyDescent="0.4">
+    <row r="20" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="9:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" spans="9:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="6"/>
@@ -755,17 +850,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165F264A-263B-4AE4-BE30-B37BD58F47A5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.3828125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="158" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -776,7 +871,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -787,7 +882,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -798,7 +893,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -809,7 +904,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -820,7 +915,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -831,7 +926,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -847,12 +942,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDF5434-4D12-4F2F-B98B-154625A9FF1F}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="173.7109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -863,7 +962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -874,7 +973,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -885,7 +984,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -896,7 +995,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -913,17 +1012,16 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CB41D5-3EB7-4F7C-BAA0-9B20DD4811C4}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5A7A86-578C-4003-85F1-B01FD2330164}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -934,7 +1032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -945,45 +1043,68 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72F519A-34E9-47C6-868B-C146DEA726AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CB41D5-3EB7-4F7C-BAA0-9B20DD4811C4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="1"/>
+    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -994,7 +1115,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1005,7 +1126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1016,15 +1137,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1033,17 +1154,17 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439DE0DC-8395-49F9-9A33-3B799989CDF9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72F519A-34E9-47C6-868B-C146DEA726AE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.3046875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.53515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.15234375" style="1"/>
+    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1054,7 +1175,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1065,18 +1186,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1093,15 +1214,17 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC6C784-F6B5-426A-A91D-7FBF6EF20C65}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439DE0DC-8395-49F9-9A33-3B799989CDF9}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.3046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1112,18 +1235,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1134,7 +1257,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1151,15 +1274,73 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC6C784-F6B5-426A-A91D-7FBF6EF20C65}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9083A037-5F1C-4F1B-BC9C-BD3BCDD5C4F5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1170,7 +1351,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1181,7 +1362,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1192,7 +1373,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1203,7 +1384,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1214,7 +1395,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1225,7 +1406,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1242,16 +1423,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8827C01F-82DB-4710-97BD-1D832235DF80}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1262,7 +1443,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1273,7 +1454,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1284,7 +1465,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1295,7 +1476,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1306,7 +1487,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1317,7 +1498,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1326,97 +1507,6 @@
       </c>
       <c r="C7" s="8" t="s">
         <v>45</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B602DAF3-EA4C-4411-83F6-DC18D5FF0624}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
-  <cols>
-    <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1425,15 +1515,15 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7AE48B-043F-4B46-920A-8E923AEFDF07}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B602DAF3-EA4C-4411-83F6-DC18D5FF0624}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1444,7 +1534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1455,18 +1545,18 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="C3" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1477,7 +1567,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1488,7 +1578,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1496,10 +1586,10 @@
         <v>29</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1507,7 +1597,7 @@
         <v>30</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C50F837A-0787-4387-83AE-0FC07562A5F0}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{470CFD18-EFB5-416E-9280-5BC32D71E995}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="9" activeTab="12" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="9" activeTab="13" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,7 @@
     <sheet name="ScheduleBiMonthly" sheetId="6" r:id="rId11"/>
     <sheet name="Form Fields" sheetId="2" r:id="rId12"/>
     <sheet name="ErrorForm" sheetId="12" r:id="rId13"/>
+    <sheet name="AwardEdition" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="62">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -186,6 +187,48 @@
   </si>
   <si>
     <t>IsFinalReport__c</t>
+  </si>
+  <si>
+    <t>IsMatchRequired__c</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>GranteeMatch__c</t>
+  </si>
+  <si>
+    <t>LaverageAllowed__c</t>
+  </si>
+  <si>
+    <t>IsProgramIncomeAnticipated__c</t>
+  </si>
+  <si>
+    <t>IsAdvancePermitted__c</t>
+  </si>
+  <si>
+    <t>IsBuildUpFunctionality__c</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>IsGoalsRequired__c</t>
+  </si>
+  <si>
+    <t>KPIsRequired__c</t>
+  </si>
+  <si>
+    <t>AreExpensesBuildIUpLevel__c</t>
+  </si>
+  <si>
+    <t>RiskAssessmentRequired__c</t>
+  </si>
+  <si>
+    <t>WBSRequired__c</t>
+  </si>
+  <si>
+    <t>FocusAreaRequired__c</t>
   </si>
 </sst>
 </file>
@@ -1011,6 +1054,163 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5A5B06-1D8F-425E-BD92-FFCEADBE1230}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C10" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5A7A86-578C-4003-85F1-B01FD2330164}">
   <dimension ref="A1:C6"/>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{470CFD18-EFB5-416E-9280-5BC32D71E995}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F319721-FE88-4D46-A922-793C8B61897E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="9" activeTab="13" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="8" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="63">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -229,6 +229,9 @@
   </si>
   <si>
     <t>FocusAreaRequired__c</t>
+  </si>
+  <si>
+    <t>cls</t>
   </si>
 </sst>
 </file>
@@ -1056,14 +1059,14 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5A5B06-1D8F-425E-BD92-FFCEADBE1230}">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1074,7 +1077,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1085,7 +1088,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1096,7 +1099,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1106,8 +1109,11 @@
       <c r="C4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="M4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1118,7 +1124,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1129,7 +1135,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1140,7 +1146,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1151,7 +1157,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1162,7 +1168,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1173,7 +1179,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1184,7 +1190,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1195,7 +1201,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1750,10 +1756,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1761,10 +1767,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -1772,10 +1778,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -1783,10 +1789,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1794,10 +1800,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>42</v>
+        <v>25</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F319721-FE88-4D46-A922-793C8B61897E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C002D01-B7AA-46F5-8E56-25C65B02DB82}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="7" activeTab="8" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="10" activeTab="15" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,9 @@
     <sheet name="ScheduleBiMonthly" sheetId="6" r:id="rId11"/>
     <sheet name="Form Fields" sheetId="2" r:id="rId12"/>
     <sheet name="ErrorForm" sheetId="12" r:id="rId13"/>
-    <sheet name="AwardEdition" sheetId="14" r:id="rId14"/>
+    <sheet name="Grant_Creation2" sheetId="15" r:id="rId14"/>
+    <sheet name="AwardEdition" sheetId="14" r:id="rId15"/>
+    <sheet name="GrantFields" sheetId="16" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="77">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -232,6 +234,48 @@
   </si>
   <si>
     <t>cls</t>
+  </si>
+  <si>
+    <t>ProjectTitle__c</t>
+  </si>
+  <si>
+    <t>GrantAbbreviation__c</t>
+  </si>
+  <si>
+    <t>GA</t>
+  </si>
+  <si>
+    <t>ProjectPeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>ProjectPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>BudgetCategoryPackage__c</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>fieldInternalOrganization__c</t>
+  </si>
+  <si>
+    <t>SAN DIEGO ELECTRICAL TRAINING TRUST</t>
+  </si>
+  <si>
+    <t>Program__c</t>
+  </si>
+  <si>
+    <t>Automation Permanent Internal Program</t>
+  </si>
+  <si>
+    <t>ExternalOrganization__c</t>
+  </si>
+  <si>
+    <t>Test Automation Organization</t>
+  </si>
+  <si>
+    <t>Automation award for Closeout</t>
   </si>
 </sst>
 </file>
@@ -1058,6 +1102,140 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C15FFD35-82F3-48DD-9A87-205E87EA7B4B}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="1"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3650</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="1"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5A5B06-1D8F-425E-BD92-FFCEADBE1230}">
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1210,6 +1388,118 @@
       </c>
       <c r="C13" t="s">
         <v>49</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE680A6-31A8-4BDC-A528-C5ADC51019BA}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C002D01-B7AA-46F5-8E56-25C65B02DB82}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB70D57A-12DA-4020-A28A-A55205612796}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="10" activeTab="15" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="11" activeTab="16" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -29,6 +29,7 @@
     <sheet name="Grant_Creation2" sheetId="15" r:id="rId14"/>
     <sheet name="AwardEdition" sheetId="14" r:id="rId15"/>
     <sheet name="GrantFields" sheetId="16" r:id="rId16"/>
+    <sheet name="GrantCreate1" sheetId="17" r:id="rId17"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="78">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -276,6 +277,9 @@
   </si>
   <si>
     <t>Automation award for Closeout</t>
+  </si>
+  <si>
+    <t>Automation award for PR</t>
   </si>
 </sst>
 </file>
@@ -1507,6 +1511,119 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DF23A2-9AAE-4637-8C96-206BD121E4D6}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="1">
+        <v>3650</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5A7A86-578C-4003-85F1-B01FD2330164}">
   <dimension ref="A1:C6"/>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Product Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB70D57A-12DA-4020-A28A-A55205612796}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53A3832-71BE-47BF-95EA-A787FDFB7EB4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="11" activeTab="16" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" firstSheet="6" activeTab="6" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="79">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -280,6 +280,9 @@
   </si>
   <si>
     <t>Automation award for PR</t>
+  </si>
+  <si>
+    <t>fieldFrequency__c</t>
   </si>
 </sst>
 </file>
@@ -658,14 +661,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756EB8E1-CDD7-4F47-B6A9-50B266C05D05}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.59765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -676,7 +679,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -687,7 +690,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -698,7 +701,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -709,7 +712,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -729,13 +732,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7AE48B-043F-4B46-920A-8E923AEFDF07}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -746,7 +749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -757,7 +760,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -768,7 +771,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -779,7 +782,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -790,7 +793,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -801,7 +804,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -820,13 +823,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6733A2-29DF-4936-8F0F-DBCC59247680}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -837,7 +840,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -848,7 +851,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -859,7 +862,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -870,7 +873,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -881,7 +884,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -892,7 +895,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -903,37 +906,37 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="3"/>
     </row>
-    <row r="17" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="17" spans="9:11" x14ac:dyDescent="0.45">
       <c r="I17" s="1"/>
       <c r="J17" s="2"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="18" spans="9:11" x14ac:dyDescent="0.45">
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="19" spans="9:11" x14ac:dyDescent="0.45">
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="20" spans="9:11" x14ac:dyDescent="0.45">
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="21" spans="9:11" x14ac:dyDescent="0.45">
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" spans="9:11" x14ac:dyDescent="0.25">
+    <row r="22" spans="9:11" x14ac:dyDescent="0.45">
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="6"/>
@@ -947,14 +950,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165F264A-263B-4AE4-BE30-B37BD58F47A5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.3984375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="158" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -965,7 +968,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -976,7 +979,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -987,7 +990,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -998,7 +1001,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1009,7 +1012,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1020,7 +1023,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1039,13 +1042,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDF5434-4D12-4F2F-B98B-154625A9FF1F}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="173.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="173.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1056,7 +1059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1067,7 +1070,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1078,7 +1081,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1089,7 +1092,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1108,13 +1111,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C15FFD35-82F3-48DD-9A87-205E87EA7B4B}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1126,7 +1129,7 @@
       </c>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1138,7 +1141,7 @@
       </c>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1150,7 +1153,7 @@
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1162,7 +1165,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1174,7 +1177,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1186,7 +1189,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1198,7 +1201,7 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1210,7 +1213,7 @@
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1222,13 +1225,13 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1242,13 +1245,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5A5B06-1D8F-425E-BD92-FFCEADBE1230}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1259,7 +1262,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1270,7 +1273,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1281,7 +1284,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1295,7 +1298,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1306,7 +1309,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1317,7 +1320,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1328,7 +1331,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1339,7 +1342,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1350,7 +1353,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1361,7 +1364,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1372,7 +1375,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1383,7 +1386,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1402,12 +1405,12 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE680A6-31A8-4BDC-A528-C5ADC51019BA}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1418,7 +1421,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1429,7 +1432,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1440,7 +1443,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1451,7 +1454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1462,7 +1465,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1473,7 +1476,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1484,7 +1487,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1495,7 +1498,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1514,13 +1517,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DF23A2-9AAE-4637-8C96-206BD121E4D6}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.73046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.1328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1531,7 +1534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1542,7 +1545,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1553,7 +1556,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1564,7 +1567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1575,7 +1578,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1586,7 +1589,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1597,7 +1600,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1608,7 +1611,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1627,14 +1630,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5A7A86-578C-4003-85F1-B01FD2330164}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1645,7 +1648,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1656,7 +1659,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1667,7 +1670,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1678,7 +1681,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1689,7 +1692,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1709,15 +1712,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CB41D5-3EB7-4F7C-BAA0-9B20DD4811C4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="11.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1728,7 +1731,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1739,7 +1742,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1750,7 +1753,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1769,15 +1772,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72F519A-34E9-47C6-868B-C146DEA726AE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="11.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1788,7 +1791,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1799,7 +1802,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1810,7 +1813,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1829,15 +1832,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439DE0DC-8395-49F9-9A33-3B799989CDF9}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="11.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.59765625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.1328125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1848,7 +1851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1859,7 +1862,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1870,7 +1873,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1889,13 +1892,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC6C784-F6B5-426A-A91D-7FBF6EF20C65}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1906,7 +1909,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1917,7 +1920,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1928,7 +1931,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1947,13 +1950,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9083A037-5F1C-4F1B-BC9C-BD3BCDD5C4F5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1964,7 +1967,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1975,18 +1978,18 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1997,7 +2000,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -2008,7 +2011,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="15.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -2019,7 +2022,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -2039,13 +2042,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8827C01F-82DB-4710-97BD-1D832235DF80}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2056,7 +2059,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -2067,7 +2070,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -2078,7 +2081,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -2089,7 +2092,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -2100,7 +2103,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="15.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -2111,7 +2114,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15.4" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -2130,13 +2133,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B602DAF3-EA4C-4411-83F6-DC18D5FF0624}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2147,7 +2150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -2158,7 +2161,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -2169,7 +2172,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -2180,7 +2183,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -2191,7 +2194,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -2202,7 +2205,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="23628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workpace-gov-grants-framework-automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F53A3832-71BE-47BF-95EA-A787FDFB7EB4}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B05645-5BDE-499F-9EFA-C429B3B32366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="10395" firstSheet="6" activeTab="6" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="11" activeTab="11" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="81">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -283,13 +283,19 @@
   </si>
   <si>
     <t>fieldFrequency__c</t>
+  </si>
+  <si>
+    <t>fieldGoverningOrganizationReportDate__c</t>
+  </si>
+  <si>
+    <t>fieldBoardInformation__c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -306,6 +312,12 @@
     <font>
       <sz val="9"/>
       <color rgb="FF222222"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF202124"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -330,7 +342,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -346,6 +358,7 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -661,14 +674,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756EB8E1-CDD7-4F47-B6A9-50B266C05D05}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.59765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.59765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -679,7 +692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -690,7 +703,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -701,7 +714,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -712,7 +725,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -732,13 +745,13 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7AE48B-043F-4B46-920A-8E923AEFDF07}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -749,7 +762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -760,7 +773,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -771,7 +784,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -782,7 +795,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -793,7 +806,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -804,7 +817,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -823,13 +836,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6733A2-29DF-4936-8F0F-DBCC59247680}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -840,7 +853,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -851,7 +864,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -862,7 +875,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -873,7 +886,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -884,7 +897,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -895,7 +908,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -906,37 +919,37 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="3"/>
     </row>
-    <row r="17" spans="9:11" x14ac:dyDescent="0.45">
+    <row r="17" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I17" s="1"/>
       <c r="J17" s="2"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="9:11" x14ac:dyDescent="0.45">
+    <row r="18" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="7"/>
     </row>
-    <row r="19" spans="9:11" x14ac:dyDescent="0.45">
+    <row r="19" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I19" s="1"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="9:11" x14ac:dyDescent="0.45">
+    <row r="20" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I20" s="1"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="9:11" x14ac:dyDescent="0.45">
+    <row r="21" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I21" s="1"/>
       <c r="J21" s="1"/>
       <c r="K21" s="6"/>
     </row>
-    <row r="22" spans="9:11" x14ac:dyDescent="0.45">
+    <row r="22" spans="9:11" x14ac:dyDescent="0.25">
       <c r="I22" s="1"/>
       <c r="J22" s="1"/>
       <c r="K22" s="6"/>
@@ -950,14 +963,14 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165F264A-263B-4AE4-BE30-B37BD58F47A5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="158" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -968,7 +981,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -979,7 +992,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -990,7 +1003,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1001,7 +1014,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1012,23 +1025,23 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
-        <v>20</v>
+      <c r="B6" s="9" t="s">
+        <v>79</v>
       </c>
       <c r="C6" s="4">
         <v>-2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
-        <v>21</v>
+      <c r="B7" s="9" t="s">
+        <v>80</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>22</v>
@@ -1042,13 +1055,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDF5434-4D12-4F2F-B98B-154625A9FF1F}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="35.265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="173.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="173.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1059,7 +1072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1070,7 +1083,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1081,7 +1094,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1092,7 +1105,7 @@
         <v>-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1111,13 +1124,13 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C15FFD35-82F3-48DD-9A87-205E87EA7B4B}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1129,7 +1142,7 @@
       </c>
       <c r="D1" s="1"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,7 +1154,7 @@
       </c>
       <c r="D2" s="1"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1153,7 +1166,7 @@
       </c>
       <c r="D3" s="1"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1165,7 +1178,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1177,7 +1190,7 @@
       </c>
       <c r="D5" s="1"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1189,7 +1202,7 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1201,7 +1214,7 @@
       </c>
       <c r="D7" s="1"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,7 +1226,7 @@
       </c>
       <c r="D8" s="1"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1225,13 +1238,13 @@
       </c>
       <c r="D9" s="1"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1245,13 +1258,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5A5B06-1D8F-425E-BD92-FFCEADBE1230}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="30.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1262,7 +1275,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1273,7 +1286,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1284,7 +1297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1298,7 +1311,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1309,7 +1322,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1320,7 +1333,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1331,7 +1344,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1342,7 +1355,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1353,7 +1366,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1364,7 +1377,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1375,7 +1388,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1386,7 +1399,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1405,12 +1418,12 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE680A6-31A8-4BDC-A528-C5ADC51019BA}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="38.1328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1421,7 +1434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1432,7 +1445,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1443,7 +1456,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1454,7 +1467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1465,7 +1478,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1476,7 +1489,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1487,7 +1500,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1498,7 +1511,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1517,13 +1530,13 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DF23A2-9AAE-4637-8C96-206BD121E4D6}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="29.73046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.1328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1534,7 +1547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1545,7 +1558,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1556,7 +1569,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -1567,7 +1580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -1578,7 +1591,7 @@
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -1589,7 +1602,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -1600,7 +1613,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
@@ -1611,7 +1624,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1630,14 +1643,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5A7A86-578C-4003-85F1-B01FD2330164}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1648,7 +1661,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1659,7 +1672,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -1670,7 +1683,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1681,7 +1694,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -1692,7 +1705,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>7</v>
       </c>
@@ -1712,15 +1725,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CB41D5-3EB7-4F7C-BAA0-9B20DD4811C4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.1328125" style="1"/>
+    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1731,7 +1744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1742,7 +1755,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1753,7 +1766,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1772,15 +1785,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72F519A-34E9-47C6-868B-C146DEA726AE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.1328125" style="1"/>
+    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1791,7 +1804,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1802,7 +1815,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1813,7 +1826,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1832,15 +1845,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439DE0DC-8395-49F9-9A33-3B799989CDF9}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.1328125" style="1"/>
+    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1851,7 +1864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1862,7 +1875,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1873,7 +1886,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1892,13 +1905,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC6C784-F6B5-426A-A91D-7FBF6EF20C65}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1909,7 +1922,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1920,7 +1933,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -1931,7 +1944,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1950,13 +1963,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9083A037-5F1C-4F1B-BC9C-BD3BCDD5C4F5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1967,7 +1980,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -1978,7 +1991,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1989,7 +2002,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -2000,7 +2013,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -2011,7 +2024,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -2022,7 +2035,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -2042,13 +2055,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8827C01F-82DB-4710-97BD-1D832235DF80}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2059,7 +2072,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -2070,7 +2083,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -2081,7 +2094,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -2092,7 +2105,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -2103,7 +2116,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -2114,7 +2127,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.4" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -2133,13 +2146,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B602DAF3-EA4C-4411-83F6-DC18D5FF0624}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2150,7 +2163,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -2161,7 +2174,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -2172,7 +2185,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -2183,7 +2196,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -2194,7 +2207,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -2205,7 +2218,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B05645-5BDE-499F-9EFA-C429B3B32366}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB66AFC0-8FD7-4A36-AFD4-3DA11A7D5912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="11" activeTab="11" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="11" activeTab="16" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="79">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -108,12 +108,6 @@
     <t>NoOfPatientsServedInQuarter__c</t>
   </si>
   <si>
-    <t>GoverningOrganizationReportDate__c</t>
-  </si>
-  <si>
-    <t>BoardInformation__c</t>
-  </si>
-  <si>
     <t>the space below, provide details of the information that was presented to the board:</t>
   </si>
   <si>
@@ -135,12 +129,6 @@
     <t>Automation Test Description</t>
   </si>
   <si>
-    <t>CalReportingStartDate__c</t>
-  </si>
-  <si>
-    <t>CalReportingEndDate__c</t>
-  </si>
-  <si>
     <t>Calendar</t>
   </si>
   <si>
@@ -289,6 +277,12 @@
   </si>
   <si>
     <t>fieldBoardInformation__c</t>
+  </si>
+  <si>
+    <t>fieldCalReportingStartDate__c</t>
+  </si>
+  <si>
+    <t>fieldCalReportingEndDate__c</t>
   </si>
 </sst>
 </file>
@@ -767,10 +761,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -778,10 +772,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -789,10 +783,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -800,10 +794,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -811,10 +805,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -822,10 +816,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -858,10 +852,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -869,10 +863,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -880,10 +874,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -891,10 +885,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -902,10 +896,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
@@ -913,10 +907,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1030,7 +1024,7 @@
         <v>14</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C6" s="4">
         <v>-2</v>
@@ -1041,10 +1035,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1098,8 +1092,8 @@
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>20</v>
+      <c r="B4" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="C4" s="4">
         <v>-2</v>
@@ -1109,11 +1103,11 @@
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>21</v>
+      <c r="B5" s="9" t="s">
+        <v>76</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1147,10 +1141,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="D2" s="1"/>
     </row>
@@ -1159,10 +1153,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D3" s="1"/>
     </row>
@@ -1171,7 +1165,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
@@ -1183,7 +1177,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C5" s="1">
         <v>3650</v>
@@ -1195,10 +1189,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D6" s="1"/>
     </row>
@@ -1207,10 +1201,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D7" s="1"/>
     </row>
@@ -1219,10 +1213,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="D8" s="1"/>
     </row>
@@ -1231,10 +1225,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D9" s="1"/>
     </row>
@@ -1280,10 +1274,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.25">
@@ -1291,7 +1285,7 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C3">
         <v>10</v>
@@ -1302,13 +1296,13 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="M4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -1316,10 +1310,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -1327,10 +1321,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -1338,10 +1332,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -1349,10 +1343,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -1360,10 +1354,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -1371,10 +1365,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -1382,10 +1376,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -1393,10 +1387,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -1404,10 +1398,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1420,6 +1414,7 @@
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1439,10 +1434,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1450,10 +1445,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1461,7 +1456,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
@@ -1472,7 +1467,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C5" s="1">
         <v>3650</v>
@@ -1483,10 +1478,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1494,10 +1489,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1505,10 +1500,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1516,10 +1511,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1552,10 +1547,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1563,10 +1558,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -1574,7 +1569,7 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="C4" s="1">
         <v>0</v>
@@ -1585,7 +1580,7 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C5" s="1">
         <v>3650</v>
@@ -1596,10 +1591,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -1607,10 +1602,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
@@ -1618,10 +1613,10 @@
         <v>14</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -1629,10 +1624,10 @@
         <v>14</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -1677,7 +1672,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>5</v>
@@ -1985,10 +1980,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -1996,10 +1991,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2007,10 +2002,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2018,10 +2013,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2029,10 +2024,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2040,10 +2035,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -2077,10 +2072,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2088,10 +2083,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2099,10 +2094,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2110,10 +2105,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2121,10 +2116,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2132,10 +2127,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2168,10 +2163,10 @@
         <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -2179,10 +2174,10 @@
         <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -2190,10 +2185,10 @@
         <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -2201,10 +2196,10 @@
         <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -2212,10 +2207,10 @@
         <v>14</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -2223,10 +2218,10 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_New_Clone\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB66AFC0-8FD7-4A36-AFD4-3DA11A7D5912}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D28D4A9-A2FD-4C55-B7B5-30AFB1328F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="11" activeTab="16" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="12" activeTab="17" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -30,6 +30,7 @@
     <sheet name="AwardEdition" sheetId="14" r:id="rId15"/>
     <sheet name="GrantFields" sheetId="16" r:id="rId16"/>
     <sheet name="GrantCreate1" sheetId="17" r:id="rId17"/>
+    <sheet name="SF428C_Form" sheetId="18" r:id="rId18"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="110">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -283,13 +284,106 @@
   </si>
   <si>
     <t>fieldCalReportingEndDate__c</t>
+  </si>
+  <si>
+    <t>fieldFederalGrantIdentifyingNumbe__c</t>
+  </si>
+  <si>
+    <t>fieldRequestFederalAgencyDispositionInstr__c</t>
+  </si>
+  <si>
+    <t>fieldOther__c</t>
+  </si>
+  <si>
+    <t>fieldRequestApprovalSF428C__c</t>
+  </si>
+  <si>
+    <t>fieldRequestApproval2SF428C__c</t>
+  </si>
+  <si>
+    <t>fieldRequestUnconditionalTransferSF428C__c</t>
+  </si>
+  <si>
+    <t>fieldRequestAcquiredEquipmentSF428C__c</t>
+  </si>
+  <si>
+    <t>fieldRetentionAcquiredEquipmentSF428C__c</t>
+  </si>
+  <si>
+    <t>fieldSaleAcquiredEquipmentSF428C__c</t>
+  </si>
+  <si>
+    <t>fieldSaleProceedsrEstimateofCurrentFai__c</t>
+  </si>
+  <si>
+    <t>(i) Sale Proceeds OR</t>
+  </si>
+  <si>
+    <t>fieldSaleProceedsMarketValue__c</t>
+  </si>
+  <si>
+    <t>fieldPercentageofFederalParticipation__c</t>
+  </si>
+  <si>
+    <t>fieldFederalShare__c</t>
+  </si>
+  <si>
+    <t>fieldSellingandHandlingAllowance__c</t>
+  </si>
+  <si>
+    <t>fieldReportLoss__c</t>
+  </si>
+  <si>
+    <t>fieldComments__c</t>
+  </si>
+  <si>
+    <t>Automation Test</t>
+  </si>
+  <si>
+    <t>fieldAgencyresponsetorequested__c</t>
+  </si>
+  <si>
+    <t>(i) Recipient request approved</t>
+  </si>
+  <si>
+    <t>fieldAgencyresponse__c</t>
+  </si>
+  <si>
+    <t>fieldDisposeinaccordance__c</t>
+  </si>
+  <si>
+    <t>fieldDisposeinaccordancewithattached__c</t>
+  </si>
+  <si>
+    <t>fieldAORSignature__c</t>
+  </si>
+  <si>
+    <t>John Mathews</t>
+  </si>
+  <si>
+    <t>fieldAcquisitionDateSF428A__c</t>
+  </si>
+  <si>
+    <t>fieldName428B__c</t>
+  </si>
+  <si>
+    <t>fieldTelephone2__c</t>
+  </si>
+  <si>
+    <t>fieldTitle__c</t>
+  </si>
+  <si>
+    <t>fieldEmailAddress__c</t>
+  </si>
+  <si>
+    <t>automation@yopmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -315,6 +409,13 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -336,8 +437,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -353,6 +453,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -668,25 +773,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{756EB8E1-CDD7-4F47-B6A9-50B266C05D05}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -697,19 +802,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
@@ -719,8 +824,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
       <c r="B5" t="s">
@@ -739,86 +844,86 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE7AE48B-043F-4B46-920A-8E923AEFDF07}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>33</v>
       </c>
     </row>
@@ -830,123 +935,105 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D6733A2-29DF-4936-8F0F-DBCC59247680}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:11">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:11">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:11">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="1:11">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="3"/>
-    </row>
-    <row r="17" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I17" s="1"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="1"/>
-    </row>
-    <row r="18" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="7"/>
-    </row>
-    <row r="19" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-    </row>
-    <row r="20" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-    </row>
-    <row r="21" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="6"/>
-    </row>
-    <row r="22" spans="9:11" x14ac:dyDescent="0.25">
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="6"/>
+    <row r="16" spans="1:11">
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" spans="10:11">
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="10:11">
+      <c r="K18" s="6"/>
+    </row>
+    <row r="21" spans="10:11">
+      <c r="K21" s="5"/>
+    </row>
+    <row r="22" spans="10:11">
+      <c r="K22" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -957,87 +1044,87 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{165F264A-263B-4AE4-BE30-B37BD58F47A5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="158" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="158" style="3" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5" s="3">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="9" t="s">
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6" s="3">
         <v>-2</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1049,64 +1136,64 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDF5434-4D12-4F2F-B98B-154625A9FF1F}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="35.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="173.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="9" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="3">
         <v>-2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="9" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1117,132 +1204,111 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C15FFD35-82F3-48DD-9A87-205E87EA7B4B}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>72</v>
       </c>
-      <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>61</v>
       </c>
-      <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>0</v>
       </c>
-      <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5">
         <v>3650</v>
       </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="7" t="s">
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>67</v>
       </c>
-      <c r="D7" s="1"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>69</v>
       </c>
-      <c r="D8" s="1"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="1" t="s">
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>71</v>
       </c>
-      <c r="D9" s="1"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1252,13 +1318,13 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5A5B06-1D8F-425E-BD92-FFCEADBE1230}">
   <dimension ref="A1:M13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1269,7 +1335,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -1280,7 +1346,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1291,7 +1357,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -1305,7 +1371,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -1316,7 +1382,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1327,7 +1393,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1338,7 +1404,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1349,7 +1415,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>14</v>
       </c>
@@ -1360,7 +1426,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -1371,7 +1437,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1382,7 +1448,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -1393,7 +1459,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -1412,108 +1478,108 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE680A6-31A8-4BDC-A528-C5ADC51019BA}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5">
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="7" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="1" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1525,189 +1591,501 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DF23A2-9AAE-4637-8C96-206BD121E4D6}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="1" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>60</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
         <v>62</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5">
         <v>3650</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
         <v>64</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="7" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="1" t="s">
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="1" t="s">
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
         <v>70</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" t="s">
         <v>71</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5CE5DD-3172-4B5D-9DF0-D4E246B7968A}">
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2">
+        <v>1567838</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="10">
+        <v>9999.99</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C13" s="11">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="10">
+        <v>9999.99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="10">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>94</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25">
+        <v>8967045891</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5A7A86-578C-4003-85F1-B01FD2330164}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>43</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1720,55 +2098,54 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CB41D5-3EB7-4F7C-BAA0-9B20DD4811C4}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1780,55 +2157,54 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72F519A-34E9-47C6-868B-C146DEA726AE}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1840,55 +2216,54 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439DE0DC-8395-49F9-9A33-3B799989CDF9}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="95.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="95.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1900,53 +2275,53 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC6C784-F6B5-426A-A91D-7FBF6EF20C65}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="106" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -1958,86 +2333,86 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9083A037-5F1C-4F1B-BC9C-BD3BCDD5C4F5}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>29</v>
       </c>
     </row>
@@ -2050,86 +2425,86 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8827C01F-82DB-4710-97BD-1D832235DF80}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="7" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
         <v>78</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="7" t="s">
         <v>41</v>
       </c>
     </row>
@@ -2141,86 +2516,86 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B602DAF3-EA4C-4411-83F6-DC18D5FF0624}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="24" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="27" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="1" t="s">
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="1" t="s">
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" t="s">
         <v>39</v>
       </c>
     </row>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_New_Clone\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D28D4A9-A2FD-4C55-B7B5-30AFB1328F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC885980-B232-4C83-BFF8-53D9B7746EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="12" activeTab="17" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="17" activeTab="20" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -31,6 +31,10 @@
     <sheet name="GrantFields" sheetId="16" r:id="rId16"/>
     <sheet name="GrantCreate1" sheetId="17" r:id="rId17"/>
     <sheet name="SF428C_Form" sheetId="18" r:id="rId18"/>
+    <sheet name="SF425_Form" sheetId="19" r:id="rId19"/>
+    <sheet name="SF425A_Form" sheetId="20" r:id="rId20"/>
+    <sheet name="SF428S_Form" sheetId="21" r:id="rId21"/>
+    <sheet name="SF428S_Details_Individual" sheetId="22" r:id="rId22"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="167">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -377,13 +381,187 @@
   </si>
   <si>
     <t>automation@yopmail.com</t>
+  </si>
+  <si>
+    <t>fieldFederalAgencySF428__c</t>
+  </si>
+  <si>
+    <t>fieldReportType__c</t>
+  </si>
+  <si>
+    <t>fieldBasisOfAccounting__c</t>
+  </si>
+  <si>
+    <t>fieldAcquiredDate__c</t>
+  </si>
+  <si>
+    <t>fieldAORDateSubmitted__c</t>
+  </si>
+  <si>
+    <t>fieldRecipientOrganizationNameSF428__c</t>
+  </si>
+  <si>
+    <t>fieldStreet1SF428__c</t>
+  </si>
+  <si>
+    <t>fieldStreet2SF428__c</t>
+  </si>
+  <si>
+    <t>fieldCitySF428__c</t>
+  </si>
+  <si>
+    <t>fieldCountySF428__c</t>
+  </si>
+  <si>
+    <t>fieldStateSf428__c</t>
+  </si>
+  <si>
+    <t>NY: New York</t>
+  </si>
+  <si>
+    <t>fieldProvinceSF428__c</t>
+  </si>
+  <si>
+    <t>NY</t>
+  </si>
+  <si>
+    <t>fieldCountrySF428__c</t>
+  </si>
+  <si>
+    <t>USA: UNITED STATES</t>
+  </si>
+  <si>
+    <t>fieldZipPostalCodeSF428__c</t>
+  </si>
+  <si>
+    <t>12345-1234</t>
+  </si>
+  <si>
+    <t>fieldRemark__c</t>
+  </si>
+  <si>
+    <t>fieldAcknowledgementSF428__c</t>
+  </si>
+  <si>
+    <t>fieldPrefix__c</t>
+  </si>
+  <si>
+    <t>Mr.</t>
+  </si>
+  <si>
+    <t>fieldFirstNameSF428__c</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>fieldMiddleNameSF428__c</t>
+  </si>
+  <si>
+    <t>Andrew</t>
+  </si>
+  <si>
+    <t>fieldLastNameSF428__c</t>
+  </si>
+  <si>
+    <t>Mathews</t>
+  </si>
+  <si>
+    <t>fieldSuffix__c</t>
+  </si>
+  <si>
+    <t>Jr.</t>
+  </si>
+  <si>
+    <t>fieldTitleSF429__c</t>
+  </si>
+  <si>
+    <t>Associate</t>
+  </si>
+  <si>
+    <t>fieldSubmittedBySF428__c</t>
+  </si>
+  <si>
+    <t>fieldTelephone__c</t>
+  </si>
+  <si>
+    <t>fieldSubmittedOn__c</t>
+  </si>
+  <si>
+    <t>Automation Test Organization</t>
+  </si>
+  <si>
+    <t>Annual</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>Street 2</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>fieldFederalAgencyandOrganizationalSF429__c</t>
+  </si>
+  <si>
+    <t>fieldDate__c</t>
+  </si>
+  <si>
+    <t>fieldAnnualReportSF428A__c</t>
+  </si>
+  <si>
+    <t>fieldFinalReportSF428B__c</t>
+  </si>
+  <si>
+    <t>fieldDispositionReportRequestSF428C__c</t>
+  </si>
+  <si>
+    <t>fieldFederalAwardNumber__c</t>
+  </si>
+  <si>
+    <t>fieldGPACQ__c</t>
+  </si>
+  <si>
+    <t>ACQ</t>
+  </si>
+  <si>
+    <t>fieldDescription__c</t>
+  </si>
+  <si>
+    <t>fieldIdentificationNumber__c</t>
+  </si>
+  <si>
+    <t>fieldConditionCode__c</t>
+  </si>
+  <si>
+    <t>fieldAcquisitionCost__c</t>
+  </si>
+  <si>
+    <t>fieldDispositionRequest__c</t>
+  </si>
+  <si>
+    <t>eulkelendwdrgyethmgfmewoi</t>
+  </si>
+  <si>
+    <t>hmuiwypyiycuhuusufutweaomknxoahqrfertvpqozrqouyvublcixbvpngikvmlruxafxmiutelrogvtdzllkqrnzxnvaskebpitcgerbanctcggvwnwyid</t>
+  </si>
+  <si>
+    <t>1 - Excellent</t>
+  </si>
+  <si>
+    <t>gefakzgrpvjjbdneasuz</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="168" formatCode="0.00;[Red]0.00"/>
+  </numFmts>
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -416,6 +594,24 @@
       <name val="JetBrains Mono"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1B1B1B"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -437,7 +633,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -457,7 +653,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1849,7 +2047,7 @@
       <c r="B13" t="s">
         <v>91</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13">
         <v>75</v>
       </c>
     </row>
@@ -2005,6 +2203,340 @@
       </c>
       <c r="C27" t="s">
         <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1958581-33A5-4F8C-84D6-84BC0930B99D}">
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C16" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C25" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C27">
+        <v>2122342342</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
+        <v>144</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2095,6 +2627,251 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785359D0-8BDB-4028-AD4B-2C0A4BB56435}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="43.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C4" s="11">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="C5" s="11"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B546E08-B445-4CFC-AE7C-A360990A58B3}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="40" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2">
+        <v>64789390</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C08315C1-DA1D-48F4-A0A8-4BB13DC3E452}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="125.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="C4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" s="13">
+        <v>9999.99</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" t="s">
+        <v>166</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CB41D5-3EB7-4F7C-BAA0-9B20DD4811C4}">
   <dimension ref="A1:C4"/>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_New_Clone\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Clone_Allocation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC885980-B232-4C83-BFF8-53D9B7746EB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53AAF800-8CA6-4A2B-9686-20ED0FF7CCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="17" activeTab="20" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="17" activeTab="18" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -31,10 +31,11 @@
     <sheet name="GrantFields" sheetId="16" r:id="rId16"/>
     <sheet name="GrantCreate1" sheetId="17" r:id="rId17"/>
     <sheet name="SF428C_Form" sheetId="18" r:id="rId18"/>
-    <sheet name="SF425_Form" sheetId="19" r:id="rId19"/>
-    <sheet name="SF425A_Form" sheetId="20" r:id="rId20"/>
-    <sheet name="SF428S_Form" sheetId="21" r:id="rId21"/>
-    <sheet name="SF428S_Details_Individual" sheetId="22" r:id="rId22"/>
+    <sheet name="SF428C_Wrong_Data" sheetId="23" r:id="rId19"/>
+    <sheet name="SF425_Form" sheetId="19" r:id="rId20"/>
+    <sheet name="SF425A_Form" sheetId="20" r:id="rId21"/>
+    <sheet name="SF428S_Form" sheetId="21" r:id="rId22"/>
+    <sheet name="SF428S_Details_Individual" sheetId="22" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="167">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -559,7 +560,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.00;[Red]0.00"/>
+    <numFmt numFmtId="164" formatCode="0.00;[Red]0.00"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -655,7 +656,7 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2212,12 +2213,12 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1958581-33A5-4F8C-84D6-84BC0930B99D}">
-  <dimension ref="A1:C29"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D527DE-E15A-4471-8743-837C127E1E6A}">
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -2236,10 +2237,10 @@
         <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" t="s">
-        <v>145</v>
+        <v>79</v>
+      </c>
+      <c r="C2">
+        <v>1567838</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2247,10 +2248,10 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" t="s">
-        <v>145</v>
+        <v>80</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -2258,10 +2259,10 @@
         <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>146</v>
+        <v>81</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2269,10 +2270,10 @@
         <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>147</v>
+        <v>82</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2280,10 +2281,10 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C6">
-        <v>30</v>
+        <v>83</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2291,10 +2292,10 @@
         <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C7">
-        <v>35</v>
+        <v>84</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -2302,10 +2303,10 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>114</v>
-      </c>
-      <c r="C8">
-        <v>40</v>
+        <v>85</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -2313,10 +2314,10 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
-      </c>
-      <c r="C9" t="s">
-        <v>145</v>
+        <v>86</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -2324,10 +2325,10 @@
         <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>116</v>
-      </c>
-      <c r="C10">
-        <v>123</v>
+        <v>87</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2335,10 +2336,10 @@
         <v>14</v>
       </c>
       <c r="B11" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11" t="s">
-        <v>148</v>
+        <v>94</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:3">
@@ -2346,10 +2347,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="C12" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" spans="1:3">
@@ -2357,10 +2358,10 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
     </row>
     <row r="14" spans="1:3">
@@ -2368,10 +2369,10 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>120</v>
-      </c>
-      <c r="C14" t="s">
-        <v>121</v>
+        <v>100</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:3">
@@ -2379,10 +2380,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" t="s">
-        <v>123</v>
+        <v>101</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:3">
@@ -2390,10 +2391,10 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>124</v>
+        <v>102</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
     </row>
     <row r="17" spans="1:3">
@@ -2401,10 +2402,10 @@
         <v>14</v>
       </c>
       <c r="B17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C17" t="s">
-        <v>127</v>
+        <v>104</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2412,10 +2413,10 @@
         <v>14</v>
       </c>
       <c r="B18" t="s">
-        <v>128</v>
+        <v>105</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2423,10 +2424,10 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>129</v>
-      </c>
-      <c r="C19" t="s">
-        <v>5</v>
+        <v>106</v>
+      </c>
+      <c r="C19">
+        <v>8967045891</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -2434,10 +2435,10 @@
         <v>14</v>
       </c>
       <c r="B20" t="s">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="C20" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -2445,103 +2446,14 @@
         <v>14</v>
       </c>
       <c r="B21" t="s">
-        <v>132</v>
+        <v>108</v>
       </c>
       <c r="C21" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" t="s">
-        <v>134</v>
-      </c>
-      <c r="C22" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" t="s">
-        <v>136</v>
-      </c>
-      <c r="C23" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" t="s">
-        <v>138</v>
-      </c>
-      <c r="C24" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" t="s">
-        <v>140</v>
-      </c>
-      <c r="C25" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" t="s">
-        <v>142</v>
-      </c>
-      <c r="C26" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" t="s">
-        <v>143</v>
-      </c>
-      <c r="C27">
-        <v>2122342342</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" t="s">
-        <v>108</v>
-      </c>
-      <c r="C28" t="s">
         <v>109</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" t="s">
-        <v>144</v>
-      </c>
-      <c r="C29">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2628,6 +2540,340 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1958581-33A5-4F8C-84D6-84BC0930B99D}">
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>114</v>
+      </c>
+      <c r="C8">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>120</v>
+      </c>
+      <c r="C14" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C16" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>130</v>
+      </c>
+      <c r="C20" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>132</v>
+      </c>
+      <c r="C21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>134</v>
+      </c>
+      <c r="C22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>136</v>
+      </c>
+      <c r="C23" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C25" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>143</v>
+      </c>
+      <c r="C27">
+        <v>2122342342</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
+        <v>144</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785359D0-8BDB-4028-AD4B-2C0A4BB56435}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2689,7 +2935,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B546E08-B445-4CFC-AE7C-A360990A58B3}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2758,7 +3004,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C08315C1-DA1D-48F4-A0A8-4BB13DC3E452}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Clone_Allocation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53AAF800-8CA6-4A2B-9686-20ED0FF7CCF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F60BD4-E92B-47C9-A16E-6E7F9EE277C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="17" activeTab="18" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="20" activeTab="23" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -36,6 +36,8 @@
     <sheet name="SF425A_Form" sheetId="20" r:id="rId21"/>
     <sheet name="SF428S_Form" sheetId="21" r:id="rId22"/>
     <sheet name="SF428S_Details_Individual" sheetId="22" r:id="rId23"/>
+    <sheet name="SF428B_Form" sheetId="24" r:id="rId24"/>
+    <sheet name="SF428B_2c_deselect" sheetId="26" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -52,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="177">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -553,6 +555,36 @@
   </si>
   <si>
     <t>gefakzgrpvjjbdneasuz</t>
+  </si>
+  <si>
+    <t>fieldFederallyownedProperty__c</t>
+  </si>
+  <si>
+    <t>fieldAcquiredEquipment__c</t>
+  </si>
+  <si>
+    <t>fieldResidualUnusedSupplies__c</t>
+  </si>
+  <si>
+    <t>fieldRequestTransfertoAward__c</t>
+  </si>
+  <si>
+    <t>fieldFederalAwardIdentifier__c</t>
+  </si>
+  <si>
+    <t>fieldRequestFederalAgency__c</t>
+  </si>
+  <si>
+    <t>fieldAcknowledgeEquipment__c</t>
+  </si>
+  <si>
+    <t>fieldTotalAmount__c</t>
+  </si>
+  <si>
+    <t>Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">automation@yopmail.com  </t>
   </si>
 </sst>
 </file>
@@ -3118,6 +3150,564 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048DF57C-BB9A-45F0-8668-498DC1298DA0}">
+  <dimension ref="A1:C27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>171</v>
+      </c>
+      <c r="C7" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>173</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C13">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>91</v>
+      </c>
+      <c r="C14">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15">
+        <v>9999.99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16">
+        <v>9999.99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C18" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C19" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>100</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>102</v>
+      </c>
+      <c r="C22" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>104</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25">
+        <v>9867589302</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>107</v>
+      </c>
+      <c r="C26" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" t="s">
+        <v>176</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD8693D5-27C5-4228-92A0-224F98BEF54A}">
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19">
+        <v>9867589302</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" t="s">
+        <v>176</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CB41D5-3EB7-4F7C-BAA0-9B20DD4811C4}">
   <dimension ref="A1:C4"/>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Clone_Allocation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F60BD4-E92B-47C9-A16E-6E7F9EE277C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F6A203-1572-4995-97EC-C0BB26C65FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="20" activeTab="23" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="25" activeTab="26" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -38,6 +38,11 @@
     <sheet name="SF428S_Details_Individual" sheetId="22" r:id="rId23"/>
     <sheet name="SF428B_Form" sheetId="24" r:id="rId24"/>
     <sheet name="SF428B_2c_deselect" sheetId="26" r:id="rId25"/>
+    <sheet name="SF428_Form" sheetId="27" r:id="rId26"/>
+    <sheet name="SF428_field_not_filled" sheetId="28" r:id="rId27"/>
+    <sheet name="SF428_Supp_not_Selected" sheetId="34" r:id="rId28"/>
+    <sheet name="SF428A_Form" sheetId="31" r:id="rId29"/>
+    <sheet name="SF428A_Federal_Property" sheetId="33" r:id="rId30"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -54,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="731" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="194">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -585,6 +590,57 @@
   </si>
   <si>
     <t xml:space="preserve">automation@yopmail.com  </t>
+  </si>
+  <si>
+    <t>Federal Agency and Organizational</t>
+  </si>
+  <si>
+    <t>fieldFederalGrantIdentifyingNumberSF428__c</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>fieldRecipientAccountNumberSF428__c</t>
+  </si>
+  <si>
+    <t>fieldSupplementalSheet__c</t>
+  </si>
+  <si>
+    <t>fieldCommentsSF428__c</t>
+  </si>
+  <si>
+    <t>fieldDateReportSubmittedSF428__c</t>
+  </si>
+  <si>
+    <t>fieldAgencyCommentsSF428__c</t>
+  </si>
+  <si>
+    <t>fieldFederalGrantSF428A__c</t>
+  </si>
+  <si>
+    <t>fieldReportTypePiclikist__c</t>
+  </si>
+  <si>
+    <t>(a) Individual (Reporting Federally-owned property for one award)</t>
+  </si>
+  <si>
+    <t>fieldReportAsOf__c</t>
+  </si>
+  <si>
+    <t>fieldSEP30__c</t>
+  </si>
+  <si>
+    <t>fieldName</t>
+  </si>
+  <si>
+    <t>fieldIdentification__c</t>
+  </si>
+  <si>
+    <t>fieldAcquisitionDate__c</t>
+  </si>
+  <si>
+    <t>30 SEP</t>
   </si>
 </sst>
 </file>
@@ -666,7 +722,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -689,6 +745,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3708,6 +3765,1042 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{702E2C7F-ACEF-451E-A257-8D7A1D64246B}">
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>181</v>
+      </c>
+      <c r="C17" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>182</v>
+      </c>
+      <c r="C18" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C19" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>132</v>
+      </c>
+      <c r="C20" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C21" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>136</v>
+      </c>
+      <c r="C22" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>140</v>
+      </c>
+      <c r="C24" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>142</v>
+      </c>
+      <c r="C25" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26">
+        <v>2122342342</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
+        <v>184</v>
+      </c>
+      <c r="C29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A18586F6-6D9E-4DD3-97F2-036CA4FFCAFA}">
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>181</v>
+      </c>
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>182</v>
+      </c>
+      <c r="C15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>132</v>
+      </c>
+      <c r="C17" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>134</v>
+      </c>
+      <c r="C18" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>136</v>
+      </c>
+      <c r="C19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>140</v>
+      </c>
+      <c r="C21" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>143</v>
+      </c>
+      <c r="C23">
+        <v>2122342342</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>183</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>184</v>
+      </c>
+      <c r="C26" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B40F3CB-DBDC-4A93-851F-37D620838A58}">
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>182</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>136</v>
+      </c>
+      <c r="C21" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25">
+        <v>2122342342</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>184</v>
+      </c>
+      <c r="C28" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7EA1CE-A458-4816-B228-83DE9640B0FE}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C5">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59CB41D5-3EB7-4F7C-BAA0-9B20DD4811C4}">
   <dimension ref="A1:C4"/>
@@ -3760,6 +4853,86 @@
       </c>
       <c r="C4" t="s">
         <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EC5DAE-E2BF-47B3-A1C9-7C4F12E126E5}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="29.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="C3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4">
+        <v>76578</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>192</v>
+      </c>
+      <c r="C5">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6">
+        <v>10000</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Clone_Allocation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F6A203-1572-4995-97EC-C0BB26C65FEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C815296C-95A0-48BF-A001-2434D9804A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="25" activeTab="26" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="23" activeTab="23" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Clone_Allocation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C815296C-95A0-48BF-A001-2434D9804A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FBFF63F-44CA-4793-9957-7EC8443EFE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="23" activeTab="23" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="33" activeTab="34" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -43,6 +43,13 @@
     <sheet name="SF428_Supp_not_Selected" sheetId="34" r:id="rId28"/>
     <sheet name="SF428A_Form" sheetId="31" r:id="rId29"/>
     <sheet name="SF428A_Federal_Property" sheetId="33" r:id="rId30"/>
+    <sheet name="SF429_Form" sheetId="35" r:id="rId31"/>
+    <sheet name="SF429A_Form" sheetId="37" r:id="rId32"/>
+    <sheet name="SF429A_Form_incorrect_data" sheetId="38" r:id="rId33"/>
+    <sheet name="SF429B_Form" sheetId="41" r:id="rId34"/>
+    <sheet name="SF429B_Form_incorrect_data" sheetId="40" r:id="rId35"/>
+    <sheet name="SF429C_Form" sheetId="42" r:id="rId36"/>
+    <sheet name="SF429C_Form_incorrect_data" sheetId="43" r:id="rId37"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -59,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="273">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -641,6 +648,243 @@
   </si>
   <si>
     <t>30 SEP</t>
+  </si>
+  <si>
+    <t>fieldFederalGrantIdentifyingNumberSF429__c</t>
+  </si>
+  <si>
+    <t>fieldRecipientOrganizationNameSF429__c</t>
+  </si>
+  <si>
+    <t>fieldReportEndDate__c</t>
+  </si>
+  <si>
+    <t>fieldAttachmentA__c</t>
+  </si>
+  <si>
+    <t>fieldAttachmentB__c</t>
+  </si>
+  <si>
+    <t>fieldAttachmentC__c</t>
+  </si>
+  <si>
+    <t>Automation test</t>
+  </si>
+  <si>
+    <t>fieldTypeorPrintedPrefix__c</t>
+  </si>
+  <si>
+    <t>fieldTypeorPrintedFirstName__c</t>
+  </si>
+  <si>
+    <t>fieldTypeorPrintedMiddleName__c</t>
+  </si>
+  <si>
+    <t>fieldTypeorPrintedLastName__c</t>
+  </si>
+  <si>
+    <t>fieldTypeorPrintedSuffix__c</t>
+  </si>
+  <si>
+    <t>fieldTypeorPrintedTitle__c</t>
+  </si>
+  <si>
+    <t>fieldEmailAddress2__c</t>
+  </si>
+  <si>
+    <t>fieldPeriodStartDate__c</t>
+  </si>
+  <si>
+    <t>fieldPeriodEndDate__c</t>
+  </si>
+  <si>
+    <t>fieldTypeOfFederalInterest__c</t>
+  </si>
+  <si>
+    <t>Renovation</t>
+  </si>
+  <si>
+    <t>fieldDescriptionofRealProperty__c</t>
+  </si>
+  <si>
+    <t>Street1</t>
+  </si>
+  <si>
+    <t>fieldZoningInformation__c</t>
+  </si>
+  <si>
+    <t>fieldGPSLocationLongitude__c</t>
+  </si>
+  <si>
+    <t>fieldGPSLocationLatitude__c</t>
+  </si>
+  <si>
+    <t>fieldLandAcreageAmount__c</t>
+  </si>
+  <si>
+    <t>fieldUnits__c</t>
+  </si>
+  <si>
+    <t>Acres</t>
+  </si>
+  <si>
+    <t>fieldSquareFootageGross__c</t>
+  </si>
+  <si>
+    <t>fieldSquareFootageUsable__c</t>
+  </si>
+  <si>
+    <t>fieldUnit2__c</t>
+  </si>
+  <si>
+    <t>Square Feet</t>
+  </si>
+  <si>
+    <t>fieldOwned__c</t>
+  </si>
+  <si>
+    <t>fieldFederalSharePercentage__c</t>
+  </si>
+  <si>
+    <t>fieldNon_FederalSharePercentage__c</t>
+  </si>
+  <si>
+    <t>fieldNonFederalShare__c</t>
+  </si>
+  <si>
+    <t>fieldHasaDeed__c</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>fieldFederallyRequiredInsurance__c</t>
+  </si>
+  <si>
+    <t>fieldEnvironmentalComplianceRequirements__c</t>
+  </si>
+  <si>
+    <t>fieldNationalHistoricPreservation__c</t>
+  </si>
+  <si>
+    <t>fieldNHPADescription__c</t>
+  </si>
+  <si>
+    <t>fieldSignificantChange__c</t>
+  </si>
+  <si>
+    <t>fieldSignificantChangeDescription__c</t>
+  </si>
+  <si>
+    <t>fieldRealPropertyDispositionStatus__c</t>
+  </si>
+  <si>
+    <t>A. Sold</t>
+  </si>
+  <si>
+    <t>fieldFundsOwed__c</t>
+  </si>
+  <si>
+    <t>fieldNetProceeds__c</t>
+  </si>
+  <si>
+    <t>fieldFederalAgencyOwes__c</t>
+  </si>
+  <si>
+    <t>fieldAElectrickWh__c</t>
+  </si>
+  <si>
+    <t>fieldBPetroleumGal__c</t>
+  </si>
+  <si>
+    <t>fieldCNaturalGascuft__c</t>
+  </si>
+  <si>
+    <t>fieldDOther__c</t>
+  </si>
+  <si>
+    <t>fieldOtherDescribe__c</t>
+  </si>
+  <si>
+    <t>fieldBtu__c</t>
+  </si>
+  <si>
+    <t>fieldSF429B__c</t>
+  </si>
+  <si>
+    <t>fieldEnvironmentalDescription__c</t>
+  </si>
+  <si>
+    <t>fieldNoneoftheAbove__c</t>
+  </si>
+  <si>
+    <t>fieldElectric429B__c</t>
+  </si>
+  <si>
+    <t>fieldPetroleum429B__c</t>
+  </si>
+  <si>
+    <t>fieldNaturalGas429B__c</t>
+  </si>
+  <si>
+    <t>fieldOther429B__c</t>
+  </si>
+  <si>
+    <t>fieldSpecify__c</t>
+  </si>
+  <si>
+    <t>Test Gas</t>
+  </si>
+  <si>
+    <t>fieldElectric__c</t>
+  </si>
+  <si>
+    <t>fieldPetroleum__c</t>
+  </si>
+  <si>
+    <t>fieldNaturalGas__c</t>
+  </si>
+  <si>
+    <t>fieldSelectunits__c</t>
+  </si>
+  <si>
+    <t>fieldSelect_units__c</t>
+  </si>
+  <si>
+    <t>fieldDescription429C__c</t>
+  </si>
+  <si>
+    <t>Autmation Test</t>
+  </si>
+  <si>
+    <t>fieldDispositionPreferenceSF429C__c</t>
+  </si>
+  <si>
+    <t>A. Sell</t>
+  </si>
+  <si>
+    <t>fieldGrantNumber__c</t>
+  </si>
+  <si>
+    <t>fieldTitleSF428__c</t>
+  </si>
+  <si>
+    <t>fieldIntendedUse__c</t>
+  </si>
+  <si>
+    <t>fieldEncumberedParties__c</t>
+  </si>
+  <si>
+    <t>fieldRequestReasons__c</t>
+  </si>
+  <si>
+    <t>fieldor_Btu_429B__c</t>
+  </si>
+  <si>
+    <t>fieldorBtu__c</t>
+  </si>
+  <si>
+    <t>fieldOtherEnergy__c</t>
   </si>
 </sst>
 </file>
@@ -722,7 +966,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -746,6 +990,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4940,6 +5187,2802 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF0C752-B8E1-4378-AC7E-8304285A9B90}">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="12">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="12">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19" s="15">
+        <v>2122342342</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>196</v>
+      </c>
+      <c r="C20">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>197</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>198</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>199</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C31" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C32" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C33" s="15">
+        <v>2122342342</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="C34" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C36" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABDEAA85-D896-403F-9A59-1E6EC90F5CC2}">
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="44.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>208</v>
+      </c>
+      <c r="C3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="C4">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>210</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C7">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C8" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="C15">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C16">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C17">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C18">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>218</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C20">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C21">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>222</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C23" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C26">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C27">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C29" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="C30" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="C31" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C32" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="C33" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C34" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="C35" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="C37">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="C38">
+        <v>8000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="C39">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C40">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C41">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C42">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>14</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C43" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3C73BB-4FB2-4E8F-8651-A6AF93AAD260}">
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="C2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="12">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C13">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15">
+        <v>-818</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C16">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C17">
+        <v>-767</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C18">
+        <v>-8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>228</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="C20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C22" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>236</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>238</v>
+      </c>
+      <c r="C24">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>239</v>
+      </c>
+      <c r="C25">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="C26">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C27">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>246</v>
+      </c>
+      <c r="C28">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C29">
+        <v>-150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>243</v>
+      </c>
+      <c r="C30">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>244</v>
+      </c>
+      <c r="C31">
+        <v>-40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7695C766-C8BF-4FC6-94BA-EF5703D41976}">
+  <dimension ref="A1:C45"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="C12">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C14">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>247</v>
+      </c>
+      <c r="C15" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>224</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C17">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C18">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="C20">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="C21">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C23">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C24">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="C25">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="C26">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C27" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="C28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="C29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="C30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>233</v>
+      </c>
+      <c r="C31" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="C34" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>170</v>
+      </c>
+      <c r="C35" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C36" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C37">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="C38">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="C39">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C40">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="C41" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C42">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>14</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="C43">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C44">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C45" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE9724B-3165-4EC7-A43C-010FD17B4AF6}">
+  <dimension ref="A1:C31"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="46.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="12">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>245</v>
+      </c>
+      <c r="C12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C13">
+        <v>-466</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C14">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C15">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C16">
+        <v>-789</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C17">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C18">
+        <v>-456</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C19">
+        <v>-74</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>231</v>
+      </c>
+      <c r="C20" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>230</v>
+      </c>
+      <c r="C21" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C22">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="C23">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>251</v>
+      </c>
+      <c r="C24">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>252</v>
+      </c>
+      <c r="C25">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="C26">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="C27">
+        <v>-400</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="C28">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="C29">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="C30">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="C31">
+        <v>-50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B0DE643-B912-4343-BD29-C8DF2689D128}">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="C3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="C12">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C14">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C15">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C17">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C18">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C21">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="C22" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="C23" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C26">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C27">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C28">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="C31" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334160A4-3B02-4876-987A-F9BF90313176}">
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="3" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="15">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="3">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12" s="3">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C13" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C15" s="3">
+        <v>-85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C16" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C17" s="3">
+        <v>-76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72F519A-34E9-47C6-868B-C146DEA726AE}">
   <dimension ref="A1:C4"/>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Clone_Allocation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FBFF63F-44CA-4793-9957-7EC8443EFE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECFAC9A-8DDA-4B3A-B5AB-D44C00D72423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="33" activeTab="34" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="25" activeTab="25" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Clone_Allocation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECFAC9A-8DDA-4B3A-B5AB-D44C00D72423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1152EC92-D5A1-42AE-B3C1-0CA77225953C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="25" activeTab="25" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="29" activeTab="30" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Clone_Allocation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1152EC92-D5A1-42AE-B3C1-0CA77225953C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3E233B-81F2-49A7-BEE5-DC77768E95C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="29" activeTab="30" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="34" activeTab="37" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -50,6 +50,7 @@
     <sheet name="SF429B_Form_incorrect_data" sheetId="40" r:id="rId35"/>
     <sheet name="SF429C_Form" sheetId="42" r:id="rId36"/>
     <sheet name="SF429C_Form_incorrect_data" sheetId="43" r:id="rId37"/>
+    <sheet name="SF271_Form" sheetId="44" r:id="rId38"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -66,7 +67,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="337">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -885,6 +886,198 @@
   </si>
   <si>
     <t>fieldOtherEnergy__c</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fieldTypeOfRequest__c                                                                                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldBasisOfRequest__c                                                                                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldFederalAgencySF428__c                                                                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldFederalAwardIdentifier__c                                                                                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldPartialPaymentRequest__c                                                                                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldFinancialAssistance__c                                                                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldPeriodStartDate__c                                                                                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldPeriodEndDate__c                                                                                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldRecipientOrganizationNameSF428__c                                                                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldStreet1SF428__c                                                                                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldStreet2SF428__c                                                                                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldCitySF428__c                                                                                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldCountySF428__c                                                                                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldStateSf428__c                                                                                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldProvinceSF428__c                                                                                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldZipPostalCodeSF428__c                                                                                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldPayeeOrganizationName__c                                                                                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldPayeeStreet1__c                                                                                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldPayeeStreet2__c                                                                                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldPayeeCity__c                                                                                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldPayeeCounty__c                                                                                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldPayeeState__c                                                                                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldPayeeProvince__c                                                                                              </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldPayeeZipCode__c                                                                                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldPrograms__c                                                                                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldFunctions__c                                                                                                  </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldActivities__c                                                                                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldProgramPercentage__c                                                                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldFunctionPercentage__c                                                                                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldActivityPercentage__c                                                                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldTotalPercentage271__c                                                                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldAcknowledgementSF428__c                                                                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldSubmittedBySF428__c                                                                                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldSubmittedOn__c                                                                                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldPrefix__c                                                                                                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldFirstNameSF428__c                                                                                             </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldMiddleNameSF428__c                                                                                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldLastNameSF428__c                                                                                               </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldSuffix__c                                                                                                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldTitleSF429__c                                                                                                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldTelephone__c                                                                                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldSignatureofAuthorized__c                                                                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldAORDateSubmitted__c                                                                                           </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldTypeorPrintedPrefix__c                                                                                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldTypeorPrintedFirstName__c                                                                                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldTypeorPrintedMiddleName__c                                                                                   </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldTypeorPrintedLastName__c                                                                                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldTypeorPrintedTitle__c                                                                                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> fieldTelephone2__c                         </t>
+  </si>
+  <si>
+    <t>Automation Organization</t>
+  </si>
+  <si>
+    <t>Street</t>
+  </si>
+  <si>
+    <t>Test Automation</t>
+  </si>
+  <si>
+    <t>Str1</t>
+  </si>
+  <si>
+    <t>Test Programs</t>
+  </si>
+  <si>
+    <t>Test Functions</t>
+  </si>
+  <si>
+    <t>Test Activities</t>
+  </si>
+  <si>
+    <t>John Matthew</t>
+  </si>
+  <si>
+    <t>rob</t>
+  </si>
+  <si>
+    <t>Matthew</t>
+  </si>
+  <si>
+    <t>rob matthew</t>
+  </si>
+  <si>
+    <t>Jesse</t>
+  </si>
+  <si>
+    <t>Johnny</t>
+  </si>
+  <si>
+    <t>Junior</t>
   </si>
 </sst>
 </file>
@@ -7983,6 +8176,570 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CE0D8F5-D394-4E57-9163-F7E6AD0835A4}">
+  <dimension ref="A1:C50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="73.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" style="3" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>274</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>275</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>278</v>
+      </c>
+      <c r="C6" s="3">
+        <v>8967589</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>279</v>
+      </c>
+      <c r="C7" s="3">
+        <v>34567</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>280</v>
+      </c>
+      <c r="C8" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>281</v>
+      </c>
+      <c r="C9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>282</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>283</v>
+      </c>
+      <c r="C11" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>284</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>285</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>286</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>287</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>288</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>289</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>290</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>291</v>
+      </c>
+      <c r="C19" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>292</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>293</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>294</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>295</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>296</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>297</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>298</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>299</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>300</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
+        <v>301</v>
+      </c>
+      <c r="C29" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" t="s">
+        <v>302</v>
+      </c>
+      <c r="C30" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" t="s">
+        <v>303</v>
+      </c>
+      <c r="C31" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" t="s">
+        <v>304</v>
+      </c>
+      <c r="C32" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" t="s">
+        <v>305</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" t="s">
+        <v>306</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" t="s">
+        <v>307</v>
+      </c>
+      <c r="C35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" t="s">
+        <v>308</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" t="s">
+        <v>309</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" t="s">
+        <v>310</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" t="s">
+        <v>311</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" t="s">
+        <v>312</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" t="s">
+        <v>313</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" t="s">
+        <v>314</v>
+      </c>
+      <c r="C42" s="3">
+        <v>9869875890</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>14</v>
+      </c>
+      <c r="B43" t="s">
+        <v>315</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44" t="s">
+        <v>316</v>
+      </c>
+      <c r="C44" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45" t="s">
+        <v>317</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46" t="s">
+        <v>318</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47" t="s">
+        <v>319</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" t="s">
+        <v>320</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" t="s">
+        <v>321</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" t="s">
+        <v>322</v>
+      </c>
+      <c r="C50" s="3">
+        <v>9869875890</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D72F519A-34E9-47C6-868B-C146DEA726AE}">
   <dimension ref="A1:C4"/>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Clone_Allocation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3E233B-81F2-49A7-BEE5-DC77768E95C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6743968A-E0EB-4D31-9A36-2E76F6803F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="34" activeTab="37" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="35" activeTab="38" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,8 @@
     <sheet name="SF429B_Form_incorrect_data" sheetId="40" r:id="rId35"/>
     <sheet name="SF429C_Form" sheetId="42" r:id="rId36"/>
     <sheet name="SF429C_Form_incorrect_data" sheetId="43" r:id="rId37"/>
-    <sheet name="SF271_Form" sheetId="44" r:id="rId38"/>
+    <sheet name="SF271_Form" sheetId="46" r:id="rId38"/>
+    <sheet name="SF271_incorrect_data" sheetId="45" r:id="rId39"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -67,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1759" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="309">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -891,153 +892,6 @@
     <t>Final</t>
   </si>
   <si>
-    <t xml:space="preserve">fieldTypeOfRequest__c                                                                                              </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldBasisOfRequest__c                                                                                             </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldFederalAgencySF428__c                                                                                        </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldFederalAwardIdentifier__c                                                                                      </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldPartialPaymentRequest__c                                                                                      </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldFinancialAssistance__c                                                                                       </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldPeriodStartDate__c                                                                                             </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldPeriodEndDate__c                                                                                              </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldRecipientOrganizationNameSF428__c                                                                             </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldStreet1SF428__c                                                                                               </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldStreet2SF428__c                                                                                             </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldCitySF428__c                                                                                                 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldCountySF428__c                                                                                                </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldStateSf428__c                                                                                                </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldProvinceSF428__c                                                                                              </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldZipPostalCodeSF428__c                                                                                          </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldPayeeOrganizationName__c                                                                                      </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldPayeeStreet1__c                                                                                               </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldPayeeStreet2__c                                                                                              </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldPayeeCity__c                                                                                                 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldPayeeCounty__c                                                                                                </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldPayeeState__c                                                                                                 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldPayeeProvince__c                                                                                              </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldPayeeZipCode__c                                                                                               </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldPrograms__c                                                                                                   </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldFunctions__c                                                                                                  </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldActivities__c                                                                                                 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldProgramPercentage__c                                                                                         </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldFunctionPercentage__c                                                                                        </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldActivityPercentage__c                                                                                         </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldTotalPercentage271__c                                                                                         </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldAcknowledgementSF428__c                                                                                       </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldSubmittedBySF428__c                                                                                           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldSubmittedOn__c                                                                                                </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldPrefix__c                                                                                                    </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldFirstNameSF428__c                                                                                             </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldMiddleNameSF428__c                                                                                            </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldLastNameSF428__c                                                                                               </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldSuffix__c                                                                                                      </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldTitleSF429__c                                                                                                 </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldTelephone__c                                                                                                   </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldSignatureofAuthorized__c                                                                                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldAORDateSubmitted__c                                                                                           </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldTypeorPrintedPrefix__c                                                                                       </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldTypeorPrintedFirstName__c                                                                                     </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldTypeorPrintedMiddleName__c                                                                                   </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldTypeorPrintedLastName__c                                                                                      </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldTypeorPrintedTitle__c                                                                                         </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> fieldTelephone2__c                         </t>
-  </si>
-  <si>
     <t>Automation Organization</t>
   </si>
   <si>
@@ -1078,6 +932,69 @@
   </si>
   <si>
     <t>Junior</t>
+  </si>
+  <si>
+    <t>fieldTypeOfRequest__c</t>
+  </si>
+  <si>
+    <t>fieldBasisOfRequest__c</t>
+  </si>
+  <si>
+    <t>fieldPartialPaymentRequest__c</t>
+  </si>
+  <si>
+    <t>FieldAPIName</t>
+  </si>
+  <si>
+    <t>fieldFinancialAssistance__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeOrganizationName__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeStreet1__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeStreet2__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeCity__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeCounty__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeState__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeProvince__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeZipCode__c</t>
+  </si>
+  <si>
+    <t>fieldPrograms__c</t>
+  </si>
+  <si>
+    <t>fieldFunctions__c</t>
+  </si>
+  <si>
+    <t>fieldActivities__c</t>
+  </si>
+  <si>
+    <t>fieldProgramPercentage__c</t>
+  </si>
+  <si>
+    <t>fieldFunctionPercentage__c</t>
+  </si>
+  <si>
+    <t>fieldActivityPercentage__c</t>
+  </si>
+  <si>
+    <t>fieldTotalPercentage271__c</t>
+  </si>
+  <si>
+    <t>fieldSignatureofAuthorized__c</t>
   </si>
 </sst>
 </file>
@@ -8177,12 +8094,12 @@
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CE0D8F5-D394-4E57-9163-F7E6AD0835A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B75E61-DAA5-4C75-9938-082F14D489D1}">
   <dimension ref="A1:C50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="73.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="40.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -8190,7 +8107,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>291</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
@@ -8200,8 +8117,8 @@
       <c r="A2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>274</v>
+      <c r="B2" s="3" t="s">
+        <v>288</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>273</v>
@@ -8211,8 +8128,8 @@
       <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="s">
-        <v>275</v>
+      <c r="B3" s="3" t="s">
+        <v>289</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>147</v>
@@ -8222,19 +8139,19 @@
       <c r="A4" t="s">
         <v>14</v>
       </c>
-      <c r="B4" t="s">
-        <v>276</v>
+      <c r="B4" s="3" t="s">
+        <v>110</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>323</v>
+        <v>274</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="B5" t="s">
-        <v>277</v>
+      <c r="B5" s="3" t="s">
+        <v>171</v>
       </c>
       <c r="C5" s="3">
         <v>1234</v>
@@ -8244,8 +8161,8 @@
       <c r="A6" t="s">
         <v>14</v>
       </c>
-      <c r="B6" t="s">
-        <v>278</v>
+      <c r="B6" s="3" t="s">
+        <v>290</v>
       </c>
       <c r="C6" s="3">
         <v>8967589</v>
@@ -8255,8 +8172,8 @@
       <c r="A7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" t="s">
-        <v>279</v>
+      <c r="B7" s="3" t="s">
+        <v>292</v>
       </c>
       <c r="C7" s="3">
         <v>34567</v>
@@ -8266,8 +8183,8 @@
       <c r="A8" t="s">
         <v>14</v>
       </c>
-      <c r="B8" t="s">
-        <v>280</v>
+      <c r="B8" s="3" t="s">
+        <v>208</v>
       </c>
       <c r="C8" s="3">
         <v>50</v>
@@ -8277,8 +8194,8 @@
       <c r="A9" t="s">
         <v>14</v>
       </c>
-      <c r="B9" t="s">
-        <v>281</v>
+      <c r="B9" s="3" t="s">
+        <v>209</v>
       </c>
       <c r="C9" s="3">
         <v>100</v>
@@ -8288,8 +8205,8 @@
       <c r="A10" t="s">
         <v>14</v>
       </c>
-      <c r="B10" t="s">
-        <v>282</v>
+      <c r="B10" s="3" t="s">
+        <v>115</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>179</v>
@@ -8299,8 +8216,8 @@
       <c r="A11" t="s">
         <v>14</v>
       </c>
-      <c r="B11" t="s">
-        <v>283</v>
+      <c r="B11" s="3" t="s">
+        <v>116</v>
       </c>
       <c r="C11" s="3">
         <v>123</v>
@@ -8310,19 +8227,19 @@
       <c r="A12" t="s">
         <v>14</v>
       </c>
-      <c r="B12" t="s">
-        <v>284</v>
+      <c r="B12" s="3" t="s">
+        <v>117</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>324</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
         <v>14</v>
       </c>
-      <c r="B13" t="s">
-        <v>285</v>
+      <c r="B13" s="3" t="s">
+        <v>118</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>123</v>
@@ -8332,8 +8249,8 @@
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="B14" t="s">
-        <v>286</v>
+      <c r="B14" s="3" t="s">
+        <v>119</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>123</v>
@@ -8343,8 +8260,8 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15" t="s">
-        <v>287</v>
+      <c r="B15" s="3" t="s">
+        <v>120</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>121</v>
@@ -8354,8 +8271,8 @@
       <c r="A16" t="s">
         <v>14</v>
       </c>
-      <c r="B16" t="s">
-        <v>288</v>
+      <c r="B16" s="3" t="s">
+        <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>123</v>
@@ -8365,8 +8282,8 @@
       <c r="A17" t="s">
         <v>14</v>
       </c>
-      <c r="B17" t="s">
-        <v>289</v>
+      <c r="B17" s="3" t="s">
+        <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>127</v>
@@ -8376,19 +8293,19 @@
       <c r="A18" t="s">
         <v>14</v>
       </c>
-      <c r="B18" t="s">
-        <v>290</v>
+      <c r="B18" s="3" t="s">
+        <v>293</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>325</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
         <v>14</v>
       </c>
-      <c r="B19" t="s">
-        <v>291</v>
+      <c r="B19" s="3" t="s">
+        <v>294</v>
       </c>
       <c r="C19" s="3">
         <v>123</v>
@@ -8398,19 +8315,19 @@
       <c r="A20" t="s">
         <v>14</v>
       </c>
-      <c r="B20" t="s">
-        <v>292</v>
+      <c r="B20" s="3" t="s">
+        <v>295</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>326</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
         <v>14</v>
       </c>
-      <c r="B21" t="s">
-        <v>293</v>
+      <c r="B21" s="3" t="s">
+        <v>296</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>123</v>
@@ -8420,8 +8337,8 @@
       <c r="A22" t="s">
         <v>14</v>
       </c>
-      <c r="B22" t="s">
-        <v>294</v>
+      <c r="B22" s="3" t="s">
+        <v>297</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>123</v>
@@ -8431,8 +8348,8 @@
       <c r="A23" t="s">
         <v>14</v>
       </c>
-      <c r="B23" t="s">
-        <v>295</v>
+      <c r="B23" s="3" t="s">
+        <v>298</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>121</v>
@@ -8442,8 +8359,8 @@
       <c r="A24" t="s">
         <v>14</v>
       </c>
-      <c r="B24" t="s">
-        <v>296</v>
+      <c r="B24" s="3" t="s">
+        <v>299</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>123</v>
@@ -8453,8 +8370,8 @@
       <c r="A25" t="s">
         <v>14</v>
       </c>
-      <c r="B25" t="s">
-        <v>297</v>
+      <c r="B25" s="3" t="s">
+        <v>300</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>127</v>
@@ -8464,41 +8381,41 @@
       <c r="A26" t="s">
         <v>14</v>
       </c>
-      <c r="B26" t="s">
-        <v>298</v>
+      <c r="B26" s="3" t="s">
+        <v>301</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>327</v>
+        <v>278</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" t="s">
         <v>14</v>
       </c>
-      <c r="B27" t="s">
-        <v>299</v>
+      <c r="B27" s="3" t="s">
+        <v>302</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>328</v>
+        <v>279</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
         <v>14</v>
       </c>
-      <c r="B28" t="s">
-        <v>300</v>
+      <c r="B28" s="3" t="s">
+        <v>303</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>329</v>
+        <v>280</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" t="s">
         <v>14</v>
       </c>
-      <c r="B29" t="s">
-        <v>301</v>
+      <c r="B29" s="3" t="s">
+        <v>304</v>
       </c>
       <c r="C29" s="3">
         <v>75</v>
@@ -8508,8 +8425,8 @@
       <c r="A30" t="s">
         <v>14</v>
       </c>
-      <c r="B30" t="s">
-        <v>302</v>
+      <c r="B30" s="3" t="s">
+        <v>305</v>
       </c>
       <c r="C30" s="3">
         <v>65</v>
@@ -8519,8 +8436,8 @@
       <c r="A31" t="s">
         <v>14</v>
       </c>
-      <c r="B31" t="s">
-        <v>303</v>
+      <c r="B31" s="3" t="s">
+        <v>306</v>
       </c>
       <c r="C31" s="3">
         <v>85</v>
@@ -8530,8 +8447,8 @@
       <c r="A32" t="s">
         <v>14</v>
       </c>
-      <c r="B32" t="s">
-        <v>304</v>
+      <c r="B32" s="3" t="s">
+        <v>307</v>
       </c>
       <c r="C32" s="3">
         <v>55</v>
@@ -8541,8 +8458,8 @@
       <c r="A33" t="s">
         <v>14</v>
       </c>
-      <c r="B33" t="s">
-        <v>305</v>
+      <c r="B33" s="3" t="s">
+        <v>129</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>5</v>
@@ -8552,19 +8469,19 @@
       <c r="A34" t="s">
         <v>14</v>
       </c>
-      <c r="B34" t="s">
-        <v>306</v>
+      <c r="B34" s="3" t="s">
+        <v>142</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>330</v>
+        <v>281</v>
       </c>
     </row>
     <row r="35" spans="1:3">
       <c r="A35" t="s">
         <v>14</v>
       </c>
-      <c r="B35" t="s">
-        <v>307</v>
+      <c r="B35" s="3" t="s">
+        <v>144</v>
       </c>
       <c r="C35" s="3">
         <v>0</v>
@@ -8574,8 +8491,8 @@
       <c r="A36" t="s">
         <v>14</v>
       </c>
-      <c r="B36" t="s">
-        <v>308</v>
+      <c r="B36" s="3" t="s">
+        <v>130</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>131</v>
@@ -8585,8 +8502,8 @@
       <c r="A37" t="s">
         <v>14</v>
       </c>
-      <c r="B37" t="s">
-        <v>309</v>
+      <c r="B37" s="3" t="s">
+        <v>132</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>133</v>
@@ -8596,30 +8513,30 @@
       <c r="A38" t="s">
         <v>14</v>
       </c>
-      <c r="B38" t="s">
-        <v>310</v>
+      <c r="B38" s="3" t="s">
+        <v>134</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>331</v>
+        <v>282</v>
       </c>
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
         <v>14</v>
       </c>
-      <c r="B39" t="s">
-        <v>311</v>
+      <c r="B39" s="3" t="s">
+        <v>136</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>332</v>
+        <v>283</v>
       </c>
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
         <v>14</v>
       </c>
-      <c r="B40" t="s">
-        <v>312</v>
+      <c r="B40" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>139</v>
@@ -8629,8 +8546,8 @@
       <c r="A41" t="s">
         <v>14</v>
       </c>
-      <c r="B41" t="s">
-        <v>313</v>
+      <c r="B41" s="3" t="s">
+        <v>140</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>141</v>
@@ -8640,8 +8557,8 @@
       <c r="A42" t="s">
         <v>14</v>
       </c>
-      <c r="B42" t="s">
-        <v>314</v>
+      <c r="B42" s="3" t="s">
+        <v>143</v>
       </c>
       <c r="C42" s="3">
         <v>9869875890</v>
@@ -8651,19 +8568,19 @@
       <c r="A43" t="s">
         <v>14</v>
       </c>
-      <c r="B43" t="s">
-        <v>315</v>
+      <c r="B43" s="3" t="s">
+        <v>308</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>333</v>
+        <v>284</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
         <v>14</v>
       </c>
-      <c r="B44" t="s">
-        <v>316</v>
+      <c r="B44" s="3" t="s">
+        <v>114</v>
       </c>
       <c r="C44" s="3">
         <v>20</v>
@@ -8673,8 +8590,8 @@
       <c r="A45" t="s">
         <v>14</v>
       </c>
-      <c r="B45" t="s">
-        <v>317</v>
+      <c r="B45" s="3" t="s">
+        <v>201</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>131</v>
@@ -8684,55 +8601,432 @@
       <c r="A46" t="s">
         <v>14</v>
       </c>
-      <c r="B46" t="s">
-        <v>318</v>
+      <c r="B46" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>334</v>
+        <v>285</v>
       </c>
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
         <v>14</v>
       </c>
-      <c r="B47" t="s">
-        <v>319</v>
+      <c r="B47" s="3" t="s">
+        <v>203</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>335</v>
+        <v>286</v>
       </c>
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
         <v>14</v>
       </c>
-      <c r="B48" t="s">
-        <v>320</v>
+      <c r="B48" s="3" t="s">
+        <v>204</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>331</v>
+        <v>282</v>
       </c>
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
         <v>14</v>
       </c>
-      <c r="B49" t="s">
-        <v>321</v>
+      <c r="B49" s="3" t="s">
+        <v>206</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>336</v>
+        <v>287</v>
       </c>
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
         <v>14</v>
       </c>
-      <c r="B50" t="s">
-        <v>322</v>
+      <c r="B50" s="3" t="s">
+        <v>106</v>
       </c>
       <c r="C50" s="3">
         <v>9869875890</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92F13134-7D58-41D3-85C8-A2B7688C4794}">
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C6" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="3">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>293</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>294</v>
+      </c>
+      <c r="C16" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>295</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>297</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>298</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>299</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>300</v>
+      </c>
+      <c r="C22" s="3">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>301</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>302</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>303</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>304</v>
+      </c>
+      <c r="C26" s="3">
+        <v>-75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>305</v>
+      </c>
+      <c r="C27" s="3">
+        <v>-65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>306</v>
+      </c>
+      <c r="C28" s="3">
+        <v>-85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
+        <v>307</v>
+      </c>
+      <c r="C29" s="3">
+        <v>-55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" t="s">
+        <v>308</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" s="3">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Clone_Allocation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6743968A-E0EB-4D31-9A36-2E76F6803F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B29898-1937-483A-AD2F-AC155DB4E0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="35" activeTab="38" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="10" activeTab="12" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -25,33 +25,38 @@
     <sheet name="ScheduleSemiAnnually" sheetId="5" r:id="rId10"/>
     <sheet name="ScheduleBiMonthly" sheetId="6" r:id="rId11"/>
     <sheet name="Form Fields" sheetId="2" r:id="rId12"/>
-    <sheet name="ErrorForm" sheetId="12" r:id="rId13"/>
-    <sheet name="Grant_Creation2" sheetId="15" r:id="rId14"/>
-    <sheet name="AwardEdition" sheetId="14" r:id="rId15"/>
-    <sheet name="GrantFields" sheetId="16" r:id="rId16"/>
-    <sheet name="GrantCreate1" sheetId="17" r:id="rId17"/>
-    <sheet name="SF428C_Form" sheetId="18" r:id="rId18"/>
-    <sheet name="SF428C_Wrong_Data" sheetId="23" r:id="rId19"/>
-    <sheet name="SF425_Form" sheetId="19" r:id="rId20"/>
-    <sheet name="SF425A_Form" sheetId="20" r:id="rId21"/>
-    <sheet name="SF428S_Form" sheetId="21" r:id="rId22"/>
-    <sheet name="SF428S_Details_Individual" sheetId="22" r:id="rId23"/>
-    <sheet name="SF428B_Form" sheetId="24" r:id="rId24"/>
-    <sheet name="SF428B_2c_deselect" sheetId="26" r:id="rId25"/>
-    <sheet name="SF428_Form" sheetId="27" r:id="rId26"/>
-    <sheet name="SF428_field_not_filled" sheetId="28" r:id="rId27"/>
-    <sheet name="SF428_Supp_not_Selected" sheetId="34" r:id="rId28"/>
-    <sheet name="SF428A_Form" sheetId="31" r:id="rId29"/>
-    <sheet name="SF428A_Federal_Property" sheetId="33" r:id="rId30"/>
-    <sheet name="SF429_Form" sheetId="35" r:id="rId31"/>
-    <sheet name="SF429A_Form" sheetId="37" r:id="rId32"/>
-    <sheet name="SF429A_Form_incorrect_data" sheetId="38" r:id="rId33"/>
-    <sheet name="SF429B_Form" sheetId="41" r:id="rId34"/>
-    <sheet name="SF429B_Form_incorrect_data" sheetId="40" r:id="rId35"/>
-    <sheet name="SF429C_Form" sheetId="42" r:id="rId36"/>
-    <sheet name="SF429C_Form_incorrect_data" sheetId="43" r:id="rId37"/>
-    <sheet name="SF271_Form" sheetId="46" r:id="rId38"/>
-    <sheet name="SF271_incorrect_data" sheetId="45" r:id="rId39"/>
+    <sheet name="Comm_half_fill" sheetId="52" r:id="rId13"/>
+    <sheet name="ErrorForm" sheetId="12" r:id="rId14"/>
+    <sheet name="Grant_Creation2" sheetId="15" r:id="rId15"/>
+    <sheet name="AwardEdition" sheetId="14" r:id="rId16"/>
+    <sheet name="GrantFields" sheetId="16" r:id="rId17"/>
+    <sheet name="GrantCreate1" sheetId="17" r:id="rId18"/>
+    <sheet name="SF428C_Form" sheetId="18" r:id="rId19"/>
+    <sheet name="SF428C_half_fill" sheetId="47" r:id="rId20"/>
+    <sheet name="SF428C_Wrong_Data" sheetId="23" r:id="rId21"/>
+    <sheet name="SF425_Form" sheetId="19" r:id="rId22"/>
+    <sheet name="SF425A_Form" sheetId="20" r:id="rId23"/>
+    <sheet name="SF428S_Form" sheetId="21" r:id="rId24"/>
+    <sheet name="SF428S_Details_Individual" sheetId="22" r:id="rId25"/>
+    <sheet name="SF428B_Form" sheetId="24" r:id="rId26"/>
+    <sheet name="SF428B_2c_deselect" sheetId="26" r:id="rId27"/>
+    <sheet name="SF428_Form" sheetId="27" r:id="rId28"/>
+    <sheet name="SF428_field_not_filled" sheetId="28" r:id="rId29"/>
+    <sheet name="SF428_Supp_not_Selected" sheetId="34" r:id="rId30"/>
+    <sheet name="SF428A_Form" sheetId="31" r:id="rId31"/>
+    <sheet name="SF428A_Federal_Property" sheetId="33" r:id="rId32"/>
+    <sheet name="SF429_Form" sheetId="35" r:id="rId33"/>
+    <sheet name="SF429_half_fill" sheetId="51" r:id="rId34"/>
+    <sheet name="SF429A_Form" sheetId="37" r:id="rId35"/>
+    <sheet name="SF429A_Form_incorrect_data" sheetId="38" r:id="rId36"/>
+    <sheet name="SF429B_Form" sheetId="41" r:id="rId37"/>
+    <sheet name="SF429B_half_fill" sheetId="49" r:id="rId38"/>
+    <sheet name="SF429B_Form_incorrect_data" sheetId="40" r:id="rId39"/>
+    <sheet name="SF429C_Form" sheetId="42" r:id="rId40"/>
+    <sheet name="SF429C_half_fill" sheetId="50" r:id="rId41"/>
+    <sheet name="SF429C_Form_incorrect_data" sheetId="43" r:id="rId42"/>
+    <sheet name="SF271_Form" sheetId="46" r:id="rId43"/>
+    <sheet name="SF271_incorrect_data" sheetId="45" r:id="rId44"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -68,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1846" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="309">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -1779,6 +1784,86 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C922EE-7D55-45ED-84C0-E643E295F423}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="173.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="3">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDF5434-4D12-4F2F-B98B-154625A9FF1F}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1847,7 +1932,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C15FFD35-82F3-48DD-9A87-205E87EA7B4B}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1960,7 +2045,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5A5B06-1D8F-425E-BD92-FFCEADBE1230}">
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2120,7 +2205,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE680A6-31A8-4BDC-A528-C5ADC51019BA}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2233,7 +2318,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DF23A2-9AAE-4637-8C96-206BD121E4D6}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2346,7 +2431,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5CE5DD-3172-4B5D-9DF0-D4E246B7968A}">
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2655,251 +2740,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D527DE-E15A-4471-8743-837C127E1E6A}">
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2">
-        <v>1567838</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
-        <v>106</v>
-      </c>
-      <c r="C19">
-        <v>8967045891</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" t="s">
-        <v>109</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2986,6 +2826,287 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB2637BC-983B-4C46-AEC7-148BA71B263A}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2">
+        <v>1567838</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D527DE-E15A-4471-8743-837C127E1E6A}">
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2">
+        <v>1567838</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19">
+        <v>8967045891</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1958581-33A5-4F8C-84D6-84BC0930B99D}">
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3319,7 +3440,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785359D0-8BDB-4028-AD4B-2C0A4BB56435}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3381,7 +3502,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B546E08-B445-4CFC-AE7C-A360990A58B3}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3450,7 +3571,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C08315C1-DA1D-48F4-A0A8-4BB13DC3E452}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3564,7 +3685,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048DF57C-BB9A-45F0-8668-498DC1298DA0}">
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3876,7 +3997,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD8693D5-27C5-4228-92A0-224F98BEF54A}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4122,7 +4243,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{702E2C7F-ACEF-451E-A257-8D7A1D64246B}">
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4456,7 +4577,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A18586F6-6D9E-4DD3-97F2-036CA4FFCAFA}">
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4748,408 +4869,6 @@
         <v>184</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B40F3CB-DBDC-4A93-851F-37D620838A58}">
-  <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C3">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>120</v>
-      </c>
-      <c r="C9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>124</v>
-      </c>
-      <c r="C11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C12" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>180</v>
-      </c>
-      <c r="C13">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>152</v>
-      </c>
-      <c r="C14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>153</v>
-      </c>
-      <c r="C15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>154</v>
-      </c>
-      <c r="C16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>182</v>
-      </c>
-      <c r="C17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>130</v>
-      </c>
-      <c r="C18" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
-        <v>132</v>
-      </c>
-      <c r="C19" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>134</v>
-      </c>
-      <c r="C20" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" t="s">
-        <v>136</v>
-      </c>
-      <c r="C21" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" t="s">
-        <v>138</v>
-      </c>
-      <c r="C22" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" t="s">
-        <v>140</v>
-      </c>
-      <c r="C23" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" t="s">
-        <v>142</v>
-      </c>
-      <c r="C24" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" t="s">
-        <v>143</v>
-      </c>
-      <c r="C25">
-        <v>2122342342</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" t="s">
-        <v>108</v>
-      </c>
-      <c r="C26" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" t="s">
-        <v>183</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" t="s">
-        <v>184</v>
-      </c>
-      <c r="C28" t="s">
-        <v>96</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7EA1CE-A458-4816-B228-83DE9640B0FE}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="C2">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="C5">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="C6" t="s">
         <v>96</v>
       </c>
     </row>
@@ -5218,6 +4937,408 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B40F3CB-DBDC-4A93-851F-37D620838A58}">
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>182</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>136</v>
+      </c>
+      <c r="C21" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25">
+        <v>2122342342</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>184</v>
+      </c>
+      <c r="C28" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7EA1CE-A458-4816-B228-83DE9640B0FE}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C5">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EC5DAE-E2BF-47B3-A1C9-7C4F12E126E5}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5297,13 +5418,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF0C752-B8E1-4378-AC7E-8304285A9B90}">
   <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5707,7 +5828,340 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8E20211-1D84-48FF-8A84-AC0AE11DA487}">
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="12">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="12">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19" s="15">
+        <v>2122342342</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C25" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" s="15">
+        <v>2122342342</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="C28" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABDEAA85-D896-403F-9A59-1E6EC90F5CC2}">
   <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6194,7 +6648,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3C73BB-4FB2-4E8F-8651-A6AF93AAD260}">
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6549,7 +7003,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7695C766-C8BF-4FC6-94BA-EF5703D41976}">
   <dimension ref="A1:C45"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7059,7 +7513,131 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89650214-A8DD-44FC-9DFA-301D63E80C53}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE9724B-3165-4EC7-A43C-010FD17B4AF6}">
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7412,1625 +7990,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B0DE643-B912-4343-BD29-C8DF2689D128}">
-  <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="C2">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="C3" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="C9" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="C12">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="C13">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="C14">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="C15">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="C17">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="C18">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="C21">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="C22" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="C23" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="C24" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="C26">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="C27">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="C28">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>14</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="C31" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>14</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>14</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="C33" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
-        <v>14</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>14</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
-        <v>14</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334160A4-3B02-4876-987A-F9BF90313176}">
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="3" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="C3" s="3">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C10" s="15">
-        <v>12345</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="C11" s="3">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="C12" s="3">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="C13" s="3">
-        <v>-700</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" s="3">
-        <v>-300</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="C15" s="3">
-        <v>-85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="C16" s="3">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="C17" s="3">
-        <v>-76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B75E61-DAA5-4C75-9938-082F14D489D1}">
-  <dimension ref="A1:C50"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="40.140625" style="3" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="C6" s="3">
-        <v>8967589</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="C7" s="3">
-        <v>34567</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="C8" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="C9" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="C11" s="3">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C19" s="3">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C29" s="3">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="C30" s="3">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>14</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="C31" s="3">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>14</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="C32" s="3">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>14</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
-        <v>14</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>14</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C35" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
-        <v>14</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="A37" t="s">
-        <v>14</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3">
-      <c r="A38" t="s">
-        <v>14</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
-      <c r="A39" t="s">
-        <v>14</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3">
-      <c r="A40" t="s">
-        <v>14</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3">
-      <c r="A41" t="s">
-        <v>14</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3">
-      <c r="A42" t="s">
-        <v>14</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C42" s="3">
-        <v>9869875890</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3">
-      <c r="A43" t="s">
-        <v>14</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3">
-      <c r="A44" t="s">
-        <v>14</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C44" s="3">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="A45" t="s">
-        <v>14</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="A46" t="s">
-        <v>14</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3">
-      <c r="A47" t="s">
-        <v>14</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
-      <c r="A48" t="s">
-        <v>14</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3">
-      <c r="A49" t="s">
-        <v>14</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" t="s">
-        <v>14</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="C50" s="3">
-        <v>9869875890</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92F13134-7D58-41D3-85C8-A2B7688C4794}">
-  <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>288</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>289</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>110</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>208</v>
-      </c>
-      <c r="C5" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>209</v>
-      </c>
-      <c r="C6" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>115</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>116</v>
-      </c>
-      <c r="C8" s="3">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>118</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>119</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>120</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>122</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C14" s="3">
-        <v>12345</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>293</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>294</v>
-      </c>
-      <c r="C16" s="3">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>295</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>296</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
-        <v>297</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>298</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" t="s">
-        <v>299</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" t="s">
-        <v>300</v>
-      </c>
-      <c r="C22" s="3">
-        <v>12345</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" t="s">
-        <v>301</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" t="s">
-        <v>302</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" t="s">
-        <v>303</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" t="s">
-        <v>304</v>
-      </c>
-      <c r="C26" s="3">
-        <v>-75</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" t="s">
-        <v>305</v>
-      </c>
-      <c r="C27" s="3">
-        <v>-65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" t="s">
-        <v>306</v>
-      </c>
-      <c r="C28" s="3">
-        <v>-85</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" t="s">
-        <v>307</v>
-      </c>
-      <c r="C29" s="3">
-        <v>-55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" t="s">
-        <v>142</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>14</v>
-      </c>
-      <c r="B31" t="s">
-        <v>144</v>
-      </c>
-      <c r="C31" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>14</v>
-      </c>
-      <c r="B32" t="s">
-        <v>308</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>14</v>
-      </c>
-      <c r="B33" t="s">
-        <v>114</v>
-      </c>
-      <c r="C33" s="3">
-        <v>20</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -9086,6 +8045,1749 @@
       </c>
       <c r="C4" t="s">
         <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B0DE643-B912-4343-BD29-C8DF2689D128}">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="C3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="C12">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C14">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C15">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C17">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C18">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C21">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="C22" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="C23" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C26">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C27">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C28">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="C31" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87CE4365-F4A6-44A6-8070-7113DA611997}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334160A4-3B02-4876-987A-F9BF90313176}">
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="3" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="15">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="3">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12" s="3">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C13" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C15" s="3">
+        <v>-85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C16" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C17" s="3">
+        <v>-76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B75E61-DAA5-4C75-9938-082F14D489D1}">
+  <dimension ref="A1:C50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="40.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" s="3">
+        <v>8967589</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" s="3">
+        <v>34567</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C8" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C19" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C29" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C30" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C31" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C32" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C42" s="3">
+        <v>9869875890</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>14</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C50" s="3">
+        <v>9869875890</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92F13134-7D58-41D3-85C8-A2B7688C4794}">
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C6" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="3">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>293</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>294</v>
+      </c>
+      <c r="C16" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>295</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>297</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>298</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>299</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>300</v>
+      </c>
+      <c r="C22" s="3">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>301</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>302</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>303</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>304</v>
+      </c>
+      <c r="C26" s="3">
+        <v>-75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>305</v>
+      </c>
+      <c r="C27" s="3">
+        <v>-65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>306</v>
+      </c>
+      <c r="C28" s="3">
+        <v>-85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
+        <v>307</v>
+      </c>
+      <c r="C29" s="3">
+        <v>-55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" t="s">
+        <v>308</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" s="3">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/ProgressReport_Field_Values.xlsx
+++ b/src/main/resources/ProgressReport_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\Product_Clone_Allocation\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6ECFAC9A-8DDA-4B3A-B5AB-D44C00D72423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B29898-1937-483A-AD2F-AC155DB4E0F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="25" activeTab="25" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="10" activeTab="12" xr2:uid="{2CF227FB-55E5-4154-93E7-6831A7625F64}"/>
   </bookViews>
   <sheets>
     <sheet name="Edition" sheetId="1" r:id="rId1"/>
@@ -25,31 +25,38 @@
     <sheet name="ScheduleSemiAnnually" sheetId="5" r:id="rId10"/>
     <sheet name="ScheduleBiMonthly" sheetId="6" r:id="rId11"/>
     <sheet name="Form Fields" sheetId="2" r:id="rId12"/>
-    <sheet name="ErrorForm" sheetId="12" r:id="rId13"/>
-    <sheet name="Grant_Creation2" sheetId="15" r:id="rId14"/>
-    <sheet name="AwardEdition" sheetId="14" r:id="rId15"/>
-    <sheet name="GrantFields" sheetId="16" r:id="rId16"/>
-    <sheet name="GrantCreate1" sheetId="17" r:id="rId17"/>
-    <sheet name="SF428C_Form" sheetId="18" r:id="rId18"/>
-    <sheet name="SF428C_Wrong_Data" sheetId="23" r:id="rId19"/>
-    <sheet name="SF425_Form" sheetId="19" r:id="rId20"/>
-    <sheet name="SF425A_Form" sheetId="20" r:id="rId21"/>
-    <sheet name="SF428S_Form" sheetId="21" r:id="rId22"/>
-    <sheet name="SF428S_Details_Individual" sheetId="22" r:id="rId23"/>
-    <sheet name="SF428B_Form" sheetId="24" r:id="rId24"/>
-    <sheet name="SF428B_2c_deselect" sheetId="26" r:id="rId25"/>
-    <sheet name="SF428_Form" sheetId="27" r:id="rId26"/>
-    <sheet name="SF428_field_not_filled" sheetId="28" r:id="rId27"/>
-    <sheet name="SF428_Supp_not_Selected" sheetId="34" r:id="rId28"/>
-    <sheet name="SF428A_Form" sheetId="31" r:id="rId29"/>
-    <sheet name="SF428A_Federal_Property" sheetId="33" r:id="rId30"/>
-    <sheet name="SF429_Form" sheetId="35" r:id="rId31"/>
-    <sheet name="SF429A_Form" sheetId="37" r:id="rId32"/>
-    <sheet name="SF429A_Form_incorrect_data" sheetId="38" r:id="rId33"/>
-    <sheet name="SF429B_Form" sheetId="41" r:id="rId34"/>
-    <sheet name="SF429B_Form_incorrect_data" sheetId="40" r:id="rId35"/>
-    <sheet name="SF429C_Form" sheetId="42" r:id="rId36"/>
-    <sheet name="SF429C_Form_incorrect_data" sheetId="43" r:id="rId37"/>
+    <sheet name="Comm_half_fill" sheetId="52" r:id="rId13"/>
+    <sheet name="ErrorForm" sheetId="12" r:id="rId14"/>
+    <sheet name="Grant_Creation2" sheetId="15" r:id="rId15"/>
+    <sheet name="AwardEdition" sheetId="14" r:id="rId16"/>
+    <sheet name="GrantFields" sheetId="16" r:id="rId17"/>
+    <sheet name="GrantCreate1" sheetId="17" r:id="rId18"/>
+    <sheet name="SF428C_Form" sheetId="18" r:id="rId19"/>
+    <sheet name="SF428C_half_fill" sheetId="47" r:id="rId20"/>
+    <sheet name="SF428C_Wrong_Data" sheetId="23" r:id="rId21"/>
+    <sheet name="SF425_Form" sheetId="19" r:id="rId22"/>
+    <sheet name="SF425A_Form" sheetId="20" r:id="rId23"/>
+    <sheet name="SF428S_Form" sheetId="21" r:id="rId24"/>
+    <sheet name="SF428S_Details_Individual" sheetId="22" r:id="rId25"/>
+    <sheet name="SF428B_Form" sheetId="24" r:id="rId26"/>
+    <sheet name="SF428B_2c_deselect" sheetId="26" r:id="rId27"/>
+    <sheet name="SF428_Form" sheetId="27" r:id="rId28"/>
+    <sheet name="SF428_field_not_filled" sheetId="28" r:id="rId29"/>
+    <sheet name="SF428_Supp_not_Selected" sheetId="34" r:id="rId30"/>
+    <sheet name="SF428A_Form" sheetId="31" r:id="rId31"/>
+    <sheet name="SF428A_Federal_Property" sheetId="33" r:id="rId32"/>
+    <sheet name="SF429_Form" sheetId="35" r:id="rId33"/>
+    <sheet name="SF429_half_fill" sheetId="51" r:id="rId34"/>
+    <sheet name="SF429A_Form" sheetId="37" r:id="rId35"/>
+    <sheet name="SF429A_Form_incorrect_data" sheetId="38" r:id="rId36"/>
+    <sheet name="SF429B_Form" sheetId="41" r:id="rId37"/>
+    <sheet name="SF429B_half_fill" sheetId="49" r:id="rId38"/>
+    <sheet name="SF429B_Form_incorrect_data" sheetId="40" r:id="rId39"/>
+    <sheet name="SF429C_Form" sheetId="42" r:id="rId40"/>
+    <sheet name="SF429C_half_fill" sheetId="50" r:id="rId41"/>
+    <sheet name="SF429C_Form_incorrect_data" sheetId="43" r:id="rId42"/>
+    <sheet name="SF271_Form" sheetId="46" r:id="rId43"/>
+    <sheet name="SF271_incorrect_data" sheetId="45" r:id="rId44"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -66,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2005" uniqueCount="309">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -885,6 +892,114 @@
   </si>
   <si>
     <t>fieldOtherEnergy__c</t>
+  </si>
+  <si>
+    <t>Final</t>
+  </si>
+  <si>
+    <t>Automation Organization</t>
+  </si>
+  <si>
+    <t>Street</t>
+  </si>
+  <si>
+    <t>Test Automation</t>
+  </si>
+  <si>
+    <t>Str1</t>
+  </si>
+  <si>
+    <t>Test Programs</t>
+  </si>
+  <si>
+    <t>Test Functions</t>
+  </si>
+  <si>
+    <t>Test Activities</t>
+  </si>
+  <si>
+    <t>John Matthew</t>
+  </si>
+  <si>
+    <t>rob</t>
+  </si>
+  <si>
+    <t>Matthew</t>
+  </si>
+  <si>
+    <t>rob matthew</t>
+  </si>
+  <si>
+    <t>Jesse</t>
+  </si>
+  <si>
+    <t>Johnny</t>
+  </si>
+  <si>
+    <t>Junior</t>
+  </si>
+  <si>
+    <t>fieldTypeOfRequest__c</t>
+  </si>
+  <si>
+    <t>fieldBasisOfRequest__c</t>
+  </si>
+  <si>
+    <t>fieldPartialPaymentRequest__c</t>
+  </si>
+  <si>
+    <t>FieldAPIName</t>
+  </si>
+  <si>
+    <t>fieldFinancialAssistance__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeOrganizationName__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeStreet1__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeStreet2__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeCity__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeCounty__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeState__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeProvince__c</t>
+  </si>
+  <si>
+    <t>fieldPayeeZipCode__c</t>
+  </si>
+  <si>
+    <t>fieldPrograms__c</t>
+  </si>
+  <si>
+    <t>fieldFunctions__c</t>
+  </si>
+  <si>
+    <t>fieldActivities__c</t>
+  </si>
+  <si>
+    <t>fieldProgramPercentage__c</t>
+  </si>
+  <si>
+    <t>fieldFunctionPercentage__c</t>
+  </si>
+  <si>
+    <t>fieldActivityPercentage__c</t>
+  </si>
+  <si>
+    <t>fieldTotalPercentage271__c</t>
+  </si>
+  <si>
+    <t>fieldSignatureofAuthorized__c</t>
   </si>
 </sst>
 </file>
@@ -1669,6 +1784,86 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3C922EE-7D55-45ED-84C0-E643E295F423}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="41" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="173.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="3">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BDDF5434-4D12-4F2F-B98B-154625A9FF1F}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1737,7 +1932,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C15FFD35-82F3-48DD-9A87-205E87EA7B4B}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -1850,7 +2045,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB5A5B06-1D8F-425E-BD92-FFCEADBE1230}">
   <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2010,7 +2205,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE680A6-31A8-4BDC-A528-C5ADC51019BA}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2123,7 +2318,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3DF23A2-9AAE-4637-8C96-206BD121E4D6}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2236,7 +2431,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D5CE5DD-3172-4B5D-9DF0-D4E246B7968A}">
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -2545,251 +2740,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D527DE-E15A-4471-8743-837C127E1E6A}">
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2">
-        <v>1567838</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>84</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>85</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>87</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>94</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>97</v>
-      </c>
-      <c r="C12" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>99</v>
-      </c>
-      <c r="C13" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>102</v>
-      </c>
-      <c r="C16" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
-        <v>106</v>
-      </c>
-      <c r="C19">
-        <v>8967045891</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" t="s">
-        <v>109</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -2876,6 +2826,287 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB2637BC-983B-4C46-AEC7-148BA71B263A}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2">
+        <v>1567838</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5D527DE-E15A-4471-8743-837C127E1E6A}">
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="43.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2">
+        <v>1567838</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>100</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>101</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>104</v>
+      </c>
+      <c r="C17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C18" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19">
+        <v>8967045891</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>107</v>
+      </c>
+      <c r="C20" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1958581-33A5-4F8C-84D6-84BC0930B99D}">
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3209,7 +3440,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{785359D0-8BDB-4028-AD4B-2C0A4BB56435}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3271,7 +3502,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B546E08-B445-4CFC-AE7C-A360990A58B3}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3340,7 +3571,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C08315C1-DA1D-48F4-A0A8-4BB13DC3E452}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3454,7 +3685,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{048DF57C-BB9A-45F0-8668-498DC1298DA0}">
   <dimension ref="A1:C27"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -3766,7 +3997,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD8693D5-27C5-4228-92A0-224F98BEF54A}">
   <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4012,7 +4243,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{702E2C7F-ACEF-451E-A257-8D7A1D64246B}">
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4346,7 +4577,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A18586F6-6D9E-4DD3-97F2-036CA4FFCAFA}">
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -4638,408 +4869,6 @@
         <v>184</v>
       </c>
       <c r="C26" t="s">
-        <v>96</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B40F3CB-DBDC-4A93-851F-37D620838A58}">
-  <dimension ref="A1:C28"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>178</v>
-      </c>
-      <c r="C3">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C5">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" t="s">
-        <v>119</v>
-      </c>
-      <c r="C8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" t="s">
-        <v>120</v>
-      </c>
-      <c r="C9" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" t="s">
-        <v>124</v>
-      </c>
-      <c r="C11" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C12" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" t="s">
-        <v>180</v>
-      </c>
-      <c r="C13">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>152</v>
-      </c>
-      <c r="C14" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>153</v>
-      </c>
-      <c r="C15" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" t="s">
-        <v>154</v>
-      </c>
-      <c r="C16" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>182</v>
-      </c>
-      <c r="C17" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" t="s">
-        <v>130</v>
-      </c>
-      <c r="C18" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" t="s">
-        <v>132</v>
-      </c>
-      <c r="C19" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" t="s">
-        <v>134</v>
-      </c>
-      <c r="C20" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" t="s">
-        <v>136</v>
-      </c>
-      <c r="C21" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" t="s">
-        <v>138</v>
-      </c>
-      <c r="C22" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" t="s">
-        <v>140</v>
-      </c>
-      <c r="C23" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" t="s">
-        <v>142</v>
-      </c>
-      <c r="C24" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" t="s">
-        <v>143</v>
-      </c>
-      <c r="C25">
-        <v>2122342342</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" t="s">
-        <v>108</v>
-      </c>
-      <c r="C26" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" t="s">
-        <v>183</v>
-      </c>
-      <c r="C27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" t="s">
-        <v>184</v>
-      </c>
-      <c r="C28" t="s">
-        <v>96</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7EA1CE-A458-4816-B228-83DE9640B0FE}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="C2">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>189</v>
-      </c>
-      <c r="C5">
-        <v>1111</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>182</v>
-      </c>
-      <c r="C6" t="s">
         <v>96</v>
       </c>
     </row>
@@ -5108,6 +4937,408 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B40F3CB-DBDC-4A93-851F-37D620838A58}">
+  <dimension ref="A1:C28"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="42.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>152</v>
+      </c>
+      <c r="C14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>153</v>
+      </c>
+      <c r="C15" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>154</v>
+      </c>
+      <c r="C16" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>182</v>
+      </c>
+      <c r="C17" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C18" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>132</v>
+      </c>
+      <c r="C19" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>136</v>
+      </c>
+      <c r="C21" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25">
+        <v>2122342342</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>184</v>
+      </c>
+      <c r="C28" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E7EA1CE-A458-4816-B228-83DE9640B0FE}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>189</v>
+      </c>
+      <c r="C5">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61EC5DAE-E2BF-47B3-A1C9-7C4F12E126E5}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5187,13 +5418,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BF0C752-B8E1-4378-AC7E-8304285A9B90}">
   <dimension ref="A1:C36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -5597,7 +5828,340 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8E20211-1D84-48FF-8A84-AC0AE11DA487}">
+  <dimension ref="A1:C29"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="45.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="C3" s="12">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C5" s="12">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C14" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19" s="15">
+        <v>2122342342</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>201</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>202</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="C25" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C27" s="15">
+        <v>2122342342</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>207</v>
+      </c>
+      <c r="C28" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="C29">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABDEAA85-D896-403F-9A59-1E6EC90F5CC2}">
   <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6084,7 +6648,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C3C73BB-4FB2-4E8F-8651-A6AF93AAD260}">
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6439,7 +7003,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7695C766-C8BF-4FC6-94BA-EF5703D41976}">
   <dimension ref="A1:C45"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -6949,7 +7513,131 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89650214-A8DD-44FC-9DFA-301D63E80C53}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE9724B-3165-4EC7-A43C-010FD17B4AF6}">
   <dimension ref="A1:C31"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7297,684 +7985,6 @@
       </c>
       <c r="C31">
         <v>-50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B0DE643-B912-4343-BD29-C8DF2689D128}">
-  <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="C2">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="C3" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="C7" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="C9" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>214</v>
-      </c>
-      <c r="C12">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>215</v>
-      </c>
-      <c r="C13">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>216</v>
-      </c>
-      <c r="C14">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="C15">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="C17">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="C18">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="C21">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="C22" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="C23" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="A24" t="s">
-        <v>14</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>212</v>
-      </c>
-      <c r="C24" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3">
-      <c r="A25" t="s">
-        <v>14</v>
-      </c>
-      <c r="B25" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="A26" t="s">
-        <v>14</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="C26">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
-      <c r="A27" t="s">
-        <v>14</v>
-      </c>
-      <c r="B27" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="C27">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
-      <c r="A28" t="s">
-        <v>14</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="C28">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3">
-      <c r="A29" t="s">
-        <v>14</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
-      <c r="A30" t="s">
-        <v>14</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3">
-      <c r="A31" t="s">
-        <v>14</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="C31" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3">
-      <c r="A32" t="s">
-        <v>14</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" t="s">
-        <v>14</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="C33" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3">
-      <c r="A34" t="s">
-        <v>14</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3">
-      <c r="A35" t="s">
-        <v>14</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="A36" t="s">
-        <v>14</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334160A4-3B02-4876-987A-F9BF90313176}">
-  <dimension ref="A1:C23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" style="3" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="C2" s="3">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>116</v>
-      </c>
-      <c r="C3" s="3">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>118</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" t="s">
-        <v>14</v>
-      </c>
-      <c r="B10" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="C10" s="15">
-        <v>12345</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>217</v>
-      </c>
-      <c r="C11" s="3">
-        <v>-500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>220</v>
-      </c>
-      <c r="C12" s="3">
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="C13" s="3">
-        <v>-700</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
-      <c r="A14" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C14" s="3">
-        <v>-300</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
-      <c r="A15" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>225</v>
-      </c>
-      <c r="C15" s="3">
-        <v>-85</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
-      <c r="A16" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="C16" s="3">
-        <v>-200</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="C17" s="3">
-        <v>-76</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="A19" t="s">
-        <v>14</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="A20" t="s">
-        <v>14</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="A21" t="s">
-        <v>14</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3">
-      <c r="A22" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>128</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -8042,6 +8052,1749 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B0DE643-B912-4343-BD29-C8DF2689D128}">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="C3" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>214</v>
+      </c>
+      <c r="C12">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>215</v>
+      </c>
+      <c r="C13">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="C14">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C15">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C17">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C18">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="C21">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>266</v>
+      </c>
+      <c r="C22" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="C23" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C25">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C26">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C27">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C28">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>234</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>248</v>
+      </c>
+      <c r="C31" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C33" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87CE4365-F4A6-44A6-8070-7113DA611997}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="27.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{334160A4-3B02-4876-987A-F9BF90313176}">
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" style="3" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C3" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="C10" s="15">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="3">
+        <v>-500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>220</v>
+      </c>
+      <c r="C12" s="3">
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>221</v>
+      </c>
+      <c r="C13" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C14" s="3">
+        <v>-300</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>225</v>
+      </c>
+      <c r="C15" s="3">
+        <v>-85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>227</v>
+      </c>
+      <c r="C16" s="3">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>226</v>
+      </c>
+      <c r="C17" s="3">
+        <v>-76</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75B75E61-DAA5-4C75-9938-082F14D489D1}">
+  <dimension ref="A1:C50"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="40.140625" style="3" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" s="3">
+        <v>8967589</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" s="3">
+        <v>34567</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C8" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C9" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C19" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C29" s="3">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C30" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="C31" s="3">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="C32" s="3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>14</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="C35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>14</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>14</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>14</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>14</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>14</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>14</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="C42" s="3">
+        <v>9869875890</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>14</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C44" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>14</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>14</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>14</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" t="s">
+        <v>14</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" t="s">
+        <v>14</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C50" s="3">
+        <v>9869875890</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92F13134-7D58-41D3-85C8-A2B7688C4794}">
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="39" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" t="s">
+        <v>288</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B6" t="s">
+        <v>209</v>
+      </c>
+      <c r="C6" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" s="3">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>293</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>294</v>
+      </c>
+      <c r="C16" s="3">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>295</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+      <c r="B18" t="s">
+        <v>296</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" t="s">
+        <v>297</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" t="s">
+        <v>298</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B21" t="s">
+        <v>299</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B22" t="s">
+        <v>300</v>
+      </c>
+      <c r="C22" s="3">
+        <v>12345</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" t="s">
+        <v>301</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" t="s">
+        <v>302</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" t="s">
+        <v>303</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" t="s">
+        <v>304</v>
+      </c>
+      <c r="C26" s="3">
+        <v>-75</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>14</v>
+      </c>
+      <c r="B27" t="s">
+        <v>305</v>
+      </c>
+      <c r="C27" s="3">
+        <v>-65</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>14</v>
+      </c>
+      <c r="B28" t="s">
+        <v>306</v>
+      </c>
+      <c r="C28" s="3">
+        <v>-85</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B29" t="s">
+        <v>307</v>
+      </c>
+      <c r="C29" s="3">
+        <v>-55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>14</v>
+      </c>
+      <c r="B30" t="s">
+        <v>142</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>14</v>
+      </c>
+      <c r="B31" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>14</v>
+      </c>
+      <c r="B32" t="s">
+        <v>308</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" s="3">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439DE0DC-8395-49F9-9A33-3B799989CDF9}">
   <dimension ref="A1:C4"/>
